--- a/data/raw/VALE3.SA.xlsx
+++ b/data/raw/VALE3.SA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,5022 +468,5002 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45833</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>46.34260559082031</v>
+        <v>49.9321403503418</v>
       </c>
       <c r="C2" t="n">
-        <v>46.4527692838093</v>
+        <v>50.65739199648389</v>
       </c>
       <c r="D2" t="n">
-        <v>45.64489753250248</v>
+        <v>49.75771420212215</v>
       </c>
       <c r="E2" t="n">
-        <v>46.1314570534078</v>
+        <v>50.5380459466279</v>
       </c>
       <c r="F2" t="n">
-        <v>23319900</v>
+        <v>13174500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45834</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>47.7380256652832</v>
+        <v>50.1065673828125</v>
       </c>
       <c r="C3" t="n">
-        <v>48.01343665140554</v>
+        <v>51.03378517791408</v>
       </c>
       <c r="D3" t="n">
-        <v>46.67310061744698</v>
+        <v>49.90459769392198</v>
       </c>
       <c r="E3" t="n">
-        <v>46.67310061744698</v>
+        <v>50.05148378528582</v>
       </c>
       <c r="F3" t="n">
-        <v>40488400</v>
+        <v>26632000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45835</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>48.53672027587891</v>
+        <v>49.61082458496094</v>
       </c>
       <c r="C4" t="n">
-        <v>48.73868997372922</v>
+        <v>50.21673013827959</v>
       </c>
       <c r="D4" t="n">
-        <v>47.65540368859885</v>
+        <v>49.34459245494683</v>
       </c>
       <c r="E4" t="n">
-        <v>47.91245348437866</v>
+        <v>50.21673013827959</v>
       </c>
       <c r="F4" t="n">
-        <v>26016900</v>
+        <v>12209400</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45838</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>48.33475494384766</v>
+        <v>50.74919128417969</v>
       </c>
       <c r="C5" t="n">
-        <v>48.68360724377143</v>
+        <v>52.43838306725864</v>
       </c>
       <c r="D5" t="n">
-        <v>48.14196409152667</v>
+        <v>50.67574999032789</v>
       </c>
       <c r="E5" t="n">
-        <v>48.4632798440344</v>
+        <v>50.804274881099</v>
       </c>
       <c r="F5" t="n">
-        <v>19961900</v>
+        <v>46597200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45839</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>48.98655700683594</v>
+        <v>51.41018295288086</v>
       </c>
       <c r="C6" t="n">
-        <v>49.30786922589</v>
+        <v>51.61215264942023</v>
       </c>
       <c r="D6" t="n">
-        <v>48.19704298054247</v>
+        <v>50.50132282049448</v>
       </c>
       <c r="E6" t="n">
-        <v>48.28884547111776</v>
+        <v>50.67575246824786</v>
       </c>
       <c r="F6" t="n">
-        <v>21844300</v>
+        <v>18313200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45840</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>50.76755523681641</v>
+        <v>50.82263565063477</v>
       </c>
       <c r="C7" t="n">
-        <v>51.13477223211537</v>
+        <v>51.32755636098657</v>
       </c>
       <c r="D7" t="n">
-        <v>49.39049675750652</v>
+        <v>50.37279503469625</v>
       </c>
       <c r="E7" t="n">
-        <v>49.39967910851144</v>
+        <v>51.28165511496197</v>
       </c>
       <c r="F7" t="n">
-        <v>63100200</v>
+        <v>15141300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45841</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>50.52886581420898</v>
+        <v>49.49147796630859</v>
       </c>
       <c r="C8" t="n">
-        <v>51.30001869008139</v>
+        <v>50.82263509881216</v>
       </c>
       <c r="D8" t="n">
-        <v>50.32689611989645</v>
+        <v>49.13344334834734</v>
       </c>
       <c r="E8" t="n">
-        <v>50.95116290046177</v>
+        <v>50.42787808361371</v>
       </c>
       <c r="F8" t="n">
-        <v>18256300</v>
+        <v>25029100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45842</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>50.67575073242188</v>
+        <v>49.94132232666016</v>
       </c>
       <c r="C9" t="n">
-        <v>50.67575073242188</v>
+        <v>50.05148602460162</v>
       </c>
       <c r="D9" t="n">
-        <v>50.26263250457885</v>
+        <v>49.49148168183456</v>
       </c>
       <c r="E9" t="n">
-        <v>50.51968228988532</v>
+        <v>49.66590782874528</v>
       </c>
       <c r="F9" t="n">
-        <v>5449600</v>
+        <v>26394100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45845</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>49.9321403503418</v>
+        <v>49.84951782226562</v>
       </c>
       <c r="C10" t="n">
-        <v>50.65739199648389</v>
+        <v>50.29935848058739</v>
       </c>
       <c r="D10" t="n">
-        <v>49.75771420212215</v>
+        <v>49.68427051937525</v>
       </c>
       <c r="E10" t="n">
-        <v>50.5380459466279</v>
+        <v>49.94132382500523</v>
       </c>
       <c r="F10" t="n">
-        <v>13174500</v>
+        <v>20252800</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45846</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>50.1065673828125</v>
+        <v>50.08820724487305</v>
       </c>
       <c r="C11" t="n">
-        <v>51.03378517791408</v>
+        <v>50.29017343600204</v>
       </c>
       <c r="D11" t="n">
-        <v>49.90459769392198</v>
+        <v>49.5465641148603</v>
       </c>
       <c r="E11" t="n">
-        <v>50.05148378528582</v>
+        <v>49.62000541107792</v>
       </c>
       <c r="F11" t="n">
-        <v>26632000</v>
+        <v>23714000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45847</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>49.61082458496094</v>
+        <v>51.45608520507812</v>
       </c>
       <c r="C12" t="n">
-        <v>50.21673013827959</v>
+        <v>52.16297565471151</v>
       </c>
       <c r="D12" t="n">
-        <v>49.34459245494683</v>
+        <v>50.8042783561318</v>
       </c>
       <c r="E12" t="n">
-        <v>50.21673013827959</v>
+        <v>50.90526320637098</v>
       </c>
       <c r="F12" t="n">
-        <v>12209400</v>
+        <v>40484000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45848</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>50.74919128417969</v>
+        <v>52.7872428894043</v>
       </c>
       <c r="C13" t="n">
-        <v>52.43838306725864</v>
+        <v>53.21872234324034</v>
       </c>
       <c r="D13" t="n">
-        <v>50.67574999032789</v>
+        <v>52.24559973532703</v>
       </c>
       <c r="E13" t="n">
-        <v>50.804274881099</v>
+        <v>52.28232213608774</v>
       </c>
       <c r="F13" t="n">
-        <v>46597200</v>
+        <v>40945900</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45849</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>51.41018295288086</v>
+        <v>52.71379852294922</v>
       </c>
       <c r="C14" t="n">
-        <v>51.61215264942023</v>
+        <v>53.15446033163282</v>
       </c>
       <c r="D14" t="n">
-        <v>50.50132282049448</v>
+        <v>52.32822381790221</v>
       </c>
       <c r="E14" t="n">
-        <v>50.67575246824786</v>
+        <v>52.74134207476752</v>
       </c>
       <c r="F14" t="n">
-        <v>18313200</v>
+        <v>17914800</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45852</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>50.82263565063477</v>
+        <v>51.89674377441406</v>
       </c>
       <c r="C15" t="n">
-        <v>51.32755636098657</v>
+        <v>52.5944553785828</v>
       </c>
       <c r="D15" t="n">
-        <v>50.37279503469625</v>
+        <v>51.67641637460142</v>
       </c>
       <c r="E15" t="n">
-        <v>51.28165511496197</v>
+        <v>52.2731396259648</v>
       </c>
       <c r="F15" t="n">
-        <v>15141300</v>
+        <v>21651200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45853</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>49.49147796630859</v>
+        <v>51.13476943969727</v>
       </c>
       <c r="C16" t="n">
-        <v>50.82263509881216</v>
+        <v>51.66723020155872</v>
       </c>
       <c r="D16" t="n">
-        <v>49.13344334834734</v>
+        <v>50.74001241702245</v>
       </c>
       <c r="E16" t="n">
-        <v>50.42787808361371</v>
+        <v>51.57542770876763</v>
       </c>
       <c r="F16" t="n">
-        <v>25029100</v>
+        <v>21918900</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45854</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>49.94132232666016</v>
+        <v>50.63903045654297</v>
       </c>
       <c r="C17" t="n">
-        <v>50.05148602460162</v>
+        <v>50.78591655459513</v>
       </c>
       <c r="D17" t="n">
-        <v>49.49148168183456</v>
+        <v>50.16164976236325</v>
       </c>
       <c r="E17" t="n">
-        <v>49.66590782874528</v>
+        <v>50.43706075845594</v>
       </c>
       <c r="F17" t="n">
-        <v>26394100</v>
+        <v>19175100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45855</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>49.84951782226562</v>
+        <v>50.3268928527832</v>
       </c>
       <c r="C18" t="n">
-        <v>50.29935848058739</v>
+        <v>51.13476807554705</v>
       </c>
       <c r="D18" t="n">
-        <v>49.68427051937525</v>
+        <v>50.28099160761219</v>
       </c>
       <c r="E18" t="n">
-        <v>49.94132382500523</v>
+        <v>50.99706083799348</v>
       </c>
       <c r="F18" t="n">
-        <v>20252800</v>
+        <v>14648700</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45856</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>50.08820724487305</v>
+        <v>49.42721557617188</v>
       </c>
       <c r="C19" t="n">
-        <v>50.29017343600204</v>
+        <v>50.20754725709185</v>
       </c>
       <c r="D19" t="n">
-        <v>49.5465641148603</v>
+        <v>48.95901726802801</v>
       </c>
       <c r="E19" t="n">
-        <v>49.62000541107792</v>
+        <v>49.86787383737803</v>
       </c>
       <c r="F19" t="n">
-        <v>23714000</v>
+        <v>35607800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45859</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>51.45608520507812</v>
+        <v>49.07836532592773</v>
       </c>
       <c r="C20" t="n">
-        <v>52.16297565471151</v>
+        <v>49.22525142951663</v>
       </c>
       <c r="D20" t="n">
-        <v>50.8042783561318</v>
+        <v>48.07770265084058</v>
       </c>
       <c r="E20" t="n">
-        <v>50.90526320637098</v>
+        <v>48.66524706519617</v>
       </c>
       <c r="F20" t="n">
-        <v>40484000</v>
+        <v>20790000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45860</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>52.7872428894043</v>
+        <v>49.3445930480957</v>
       </c>
       <c r="C21" t="n">
-        <v>53.21872234324034</v>
+        <v>50.4003392304061</v>
       </c>
       <c r="D21" t="n">
-        <v>52.24559973532703</v>
+        <v>49.17934575865511</v>
       </c>
       <c r="E21" t="n">
-        <v>52.28232213608774</v>
+        <v>49.79443366980413</v>
       </c>
       <c r="F21" t="n">
-        <v>40945900</v>
+        <v>40510900</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45861</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>52.71379852294922</v>
+        <v>49.73935317993164</v>
       </c>
       <c r="C22" t="n">
-        <v>53.15446033163282</v>
+        <v>49.94132288009651</v>
       </c>
       <c r="D22" t="n">
-        <v>52.32822381790221</v>
+        <v>49.39967973132415</v>
       </c>
       <c r="E22" t="n">
-        <v>52.74134207476752</v>
+        <v>49.93214052897582</v>
       </c>
       <c r="F22" t="n">
-        <v>17914800</v>
+        <v>16198100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45862</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>51.89674377441406</v>
+        <v>49.67508697509766</v>
       </c>
       <c r="C23" t="n">
-        <v>52.5944553785828</v>
+        <v>50.46460101383301</v>
       </c>
       <c r="D23" t="n">
-        <v>51.67641637460142</v>
+        <v>49.67508697509766</v>
       </c>
       <c r="E23" t="n">
-        <v>52.2731396259648</v>
+        <v>49.73016706949463</v>
       </c>
       <c r="F23" t="n">
-        <v>21651200</v>
+        <v>21037600</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45863</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>51.13476943969727</v>
+        <v>49.36295700073242</v>
       </c>
       <c r="C24" t="n">
-        <v>51.66723020155872</v>
+        <v>50.13410989379173</v>
       </c>
       <c r="D24" t="n">
-        <v>50.74001241702245</v>
+        <v>49.32623460057702</v>
       </c>
       <c r="E24" t="n">
-        <v>51.57542770876763</v>
+        <v>50.04230389340322</v>
       </c>
       <c r="F24" t="n">
-        <v>21918900</v>
+        <v>17954300</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45866</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>50.63903045654297</v>
+        <v>49.72098922729492</v>
       </c>
       <c r="C25" t="n">
-        <v>50.78591655459513</v>
+        <v>50.02394376077138</v>
       </c>
       <c r="D25" t="n">
-        <v>50.16164976236325</v>
+        <v>49.4823006419831</v>
       </c>
       <c r="E25" t="n">
-        <v>50.43706075845594</v>
+        <v>49.66590562974266</v>
       </c>
       <c r="F25" t="n">
-        <v>19175100</v>
+        <v>20298800</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45867</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>50.3268928527832</v>
+        <v>50.85017776489258</v>
       </c>
       <c r="C26" t="n">
-        <v>51.13476807554705</v>
+        <v>51.13477110507873</v>
       </c>
       <c r="D26" t="n">
-        <v>50.28099160761219</v>
+        <v>49.74853030531738</v>
       </c>
       <c r="E26" t="n">
-        <v>50.99706083799348</v>
+        <v>49.75771265611991</v>
       </c>
       <c r="F26" t="n">
-        <v>14648700</v>
+        <v>24205600</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45868</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>49.42721557617188</v>
+        <v>50.79509735107422</v>
       </c>
       <c r="C27" t="n">
-        <v>50.20754725709185</v>
+        <v>51.40100292475118</v>
       </c>
       <c r="D27" t="n">
-        <v>48.95901726802801</v>
+        <v>50.76755380087933</v>
       </c>
       <c r="E27" t="n">
-        <v>49.86787383737803</v>
+        <v>50.93280109388584</v>
       </c>
       <c r="F27" t="n">
-        <v>35607800</v>
+        <v>22304000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45869</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>49.07836532592773</v>
+        <v>51.32756042480469</v>
       </c>
       <c r="C28" t="n">
-        <v>49.22525142951663</v>
+        <v>51.56624902425495</v>
       </c>
       <c r="D28" t="n">
-        <v>48.07770265084058</v>
+        <v>51.13477307501322</v>
       </c>
       <c r="E28" t="n">
-        <v>48.66524706519617</v>
+        <v>51.36428282534808</v>
       </c>
       <c r="F28" t="n">
-        <v>20790000</v>
+        <v>25851300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45870</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>49.3445930480957</v>
+        <v>51.39919662475586</v>
       </c>
       <c r="C29" t="n">
-        <v>50.4003392304061</v>
+        <v>51.78880029851823</v>
       </c>
       <c r="D29" t="n">
-        <v>49.17934575865511</v>
+        <v>51.25665719231154</v>
       </c>
       <c r="E29" t="n">
-        <v>49.79443366980413</v>
+        <v>51.59874893023524</v>
       </c>
       <c r="F29" t="n">
-        <v>40510900</v>
+        <v>19720000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>49.73935317993164</v>
+        <v>50.76252365112305</v>
       </c>
       <c r="C30" t="n">
-        <v>49.94132288009651</v>
+        <v>50.94307407711057</v>
       </c>
       <c r="D30" t="n">
-        <v>49.39967973132415</v>
+        <v>50.43944104657325</v>
       </c>
       <c r="E30" t="n">
-        <v>49.93214052897582</v>
+        <v>50.88605758075742</v>
       </c>
       <c r="F30" t="n">
-        <v>16198100</v>
+        <v>42823200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>49.67508697509766</v>
+        <v>50.66749954223633</v>
       </c>
       <c r="C31" t="n">
-        <v>50.46460101383301</v>
+        <v>50.91456740033529</v>
       </c>
       <c r="D31" t="n">
-        <v>49.67508697509766</v>
+        <v>50.3634188129824</v>
       </c>
       <c r="E31" t="n">
-        <v>49.73016706949463</v>
+        <v>50.8005344081689</v>
       </c>
       <c r="F31" t="n">
-        <v>21037600</v>
+        <v>34201900</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45875</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>49.36295700073242</v>
+        <v>50.55347061157227</v>
       </c>
       <c r="C32" t="n">
-        <v>50.13410989379173</v>
+        <v>51.03809814521585</v>
       </c>
       <c r="D32" t="n">
-        <v>49.32623460057702</v>
+        <v>50.3919256837389</v>
       </c>
       <c r="E32" t="n">
-        <v>50.04230389340322</v>
+        <v>50.45844311727962</v>
       </c>
       <c r="F32" t="n">
-        <v>17954300</v>
+        <v>12733400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45876</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>49.72098922729492</v>
+        <v>50.59148025512695</v>
       </c>
       <c r="C33" t="n">
-        <v>50.02394376077138</v>
+        <v>51.00959034403842</v>
       </c>
       <c r="D33" t="n">
-        <v>49.4823006419831</v>
+        <v>50.36341789985732</v>
       </c>
       <c r="E33" t="n">
-        <v>49.66590562974266</v>
+        <v>50.84804542052907</v>
       </c>
       <c r="F33" t="n">
-        <v>20298800</v>
+        <v>17724400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45877</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>50.85017776489258</v>
+        <v>50.36341857910156</v>
       </c>
       <c r="C34" t="n">
-        <v>51.13477110507873</v>
+        <v>50.61998737289215</v>
       </c>
       <c r="D34" t="n">
-        <v>49.74853030531738</v>
+        <v>50.23038371378679</v>
       </c>
       <c r="E34" t="n">
-        <v>49.75771265611991</v>
+        <v>50.26839471099907</v>
       </c>
       <c r="F34" t="n">
-        <v>24205600</v>
+        <v>9687300</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45880</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>50.79509735107422</v>
+        <v>50.79103469848633</v>
       </c>
       <c r="C35" t="n">
-        <v>51.40100292475118</v>
+        <v>50.86705307017243</v>
       </c>
       <c r="D35" t="n">
-        <v>50.76755380087933</v>
+        <v>50.31590809443113</v>
       </c>
       <c r="E35" t="n">
-        <v>50.93280109388584</v>
+        <v>50.38242552900459</v>
       </c>
       <c r="F35" t="n">
-        <v>22304000</v>
+        <v>10813800</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45881</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>51.32756042480469</v>
+        <v>52.06437301635742</v>
       </c>
       <c r="C36" t="n">
-        <v>51.56624902425495</v>
+        <v>52.15939688514206</v>
       </c>
       <c r="D36" t="n">
-        <v>51.13477307501322</v>
+        <v>50.65799873376103</v>
       </c>
       <c r="E36" t="n">
-        <v>51.36428282534808</v>
+        <v>50.77202810128824</v>
       </c>
       <c r="F36" t="n">
-        <v>25851300</v>
+        <v>20706700</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45882</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>51.39919662475586</v>
+        <v>52.18790435791016</v>
       </c>
       <c r="C37" t="n">
-        <v>51.78880029851823</v>
+        <v>52.64402908693994</v>
       </c>
       <c r="D37" t="n">
-        <v>51.25665719231154</v>
+        <v>52.01686211568438</v>
       </c>
       <c r="E37" t="n">
-        <v>51.59874893023524</v>
+        <v>52.42546765952103</v>
       </c>
       <c r="F37" t="n">
-        <v>19720000</v>
+        <v>10397400</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45883</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>50.76252365112305</v>
+        <v>52.65353012084961</v>
       </c>
       <c r="C38" t="n">
-        <v>50.94307407711057</v>
+        <v>52.65353012084961</v>
       </c>
       <c r="D38" t="n">
-        <v>50.43944104657325</v>
+        <v>51.9598457138618</v>
       </c>
       <c r="E38" t="n">
-        <v>50.88605758075742</v>
+        <v>52.09288058301996</v>
       </c>
       <c r="F38" t="n">
-        <v>42823200</v>
+        <v>18891500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>50.66749954223633</v>
+        <v>52.62502288818359</v>
       </c>
       <c r="C39" t="n">
-        <v>50.91456740033529</v>
+        <v>52.76755869229815</v>
       </c>
       <c r="D39" t="n">
-        <v>50.3634188129824</v>
+        <v>52.37795502783314</v>
       </c>
       <c r="E39" t="n">
-        <v>50.8005344081689</v>
+        <v>52.47298252217111</v>
       </c>
       <c r="F39" t="n">
-        <v>34201900</v>
+        <v>8789100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>50.55347061157227</v>
+        <v>52.64402770996094</v>
       </c>
       <c r="C40" t="n">
-        <v>51.03809814521585</v>
+        <v>53.39472496847022</v>
       </c>
       <c r="D40" t="n">
-        <v>50.3919256837389</v>
+        <v>52.57751027724402</v>
       </c>
       <c r="E40" t="n">
-        <v>50.45844311727962</v>
+        <v>53.21417816894261</v>
       </c>
       <c r="F40" t="n">
-        <v>12733400</v>
+        <v>22059500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45888</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>50.59148025512695</v>
+        <v>52.79607009887695</v>
       </c>
       <c r="C41" t="n">
-        <v>51.00959034403842</v>
+        <v>53.05263890273721</v>
       </c>
       <c r="D41" t="n">
-        <v>50.36341789985732</v>
+        <v>52.69154166490481</v>
       </c>
       <c r="E41" t="n">
-        <v>50.84804542052907</v>
+        <v>52.72955266360893</v>
       </c>
       <c r="F41" t="n">
-        <v>17724400</v>
+        <v>13885400</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45889</v>
+        <v>45901</v>
       </c>
       <c r="B42" t="n">
-        <v>50.36341857910156</v>
+        <v>52.83407592773438</v>
       </c>
       <c r="C42" t="n">
-        <v>50.61998737289215</v>
+        <v>52.83407592773438</v>
       </c>
       <c r="D42" t="n">
-        <v>50.23038371378679</v>
+        <v>52.0833786623851</v>
       </c>
       <c r="E42" t="n">
-        <v>50.26839471099907</v>
+        <v>52.39696033020376</v>
       </c>
       <c r="F42" t="n">
-        <v>9687300</v>
+        <v>7765400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45890</v>
+        <v>45902</v>
       </c>
       <c r="B43" t="n">
-        <v>50.79103469848633</v>
+        <v>52.63452529907227</v>
       </c>
       <c r="C43" t="n">
-        <v>50.86705307017243</v>
+        <v>52.79607023150641</v>
       </c>
       <c r="D43" t="n">
-        <v>50.31590809443113</v>
+        <v>52.30193812189663</v>
       </c>
       <c r="E43" t="n">
-        <v>50.38242552900459</v>
+        <v>52.36845555733176</v>
       </c>
       <c r="F43" t="n">
-        <v>10813800</v>
+        <v>9578500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45891</v>
+        <v>45903</v>
       </c>
       <c r="B44" t="n">
-        <v>52.06437301635742</v>
+        <v>52.83407592773438</v>
       </c>
       <c r="C44" t="n">
-        <v>52.15939688514206</v>
+        <v>53.04313278956565</v>
       </c>
       <c r="D44" t="n">
-        <v>50.65799873376103</v>
+        <v>52.49198782418536</v>
       </c>
       <c r="E44" t="n">
-        <v>50.77202810128824</v>
+        <v>52.63452362776539</v>
       </c>
       <c r="F44" t="n">
-        <v>20706700</v>
+        <v>11832100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45894</v>
+        <v>45904</v>
       </c>
       <c r="B45" t="n">
-        <v>52.18790435791016</v>
+        <v>52.93860244750977</v>
       </c>
       <c r="C45" t="n">
-        <v>52.64402908693994</v>
+        <v>53.366217092669</v>
       </c>
       <c r="D45" t="n">
-        <v>52.01686211568438</v>
+        <v>52.78656208755628</v>
       </c>
       <c r="E45" t="n">
-        <v>52.42546765952103</v>
+        <v>53.07163730935306</v>
       </c>
       <c r="F45" t="n">
-        <v>10397400</v>
+        <v>8442100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45895</v>
+        <v>45905</v>
       </c>
       <c r="B46" t="n">
-        <v>52.65353012084961</v>
+        <v>53.42323684692383</v>
       </c>
       <c r="C46" t="n">
-        <v>52.65353012084961</v>
+        <v>53.85084789324807</v>
       </c>
       <c r="D46" t="n">
-        <v>51.9598457138618</v>
+        <v>53.23318547915287</v>
       </c>
       <c r="E46" t="n">
-        <v>52.09288058301996</v>
+        <v>53.4042313476539</v>
       </c>
       <c r="F46" t="n">
-        <v>18891500</v>
+        <v>14014700</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45896</v>
+        <v>45908</v>
       </c>
       <c r="B47" t="n">
-        <v>52.62502288818359</v>
+        <v>53.55627059936523</v>
       </c>
       <c r="C47" t="n">
-        <v>52.76755869229815</v>
+        <v>53.80333483486235</v>
       </c>
       <c r="D47" t="n">
-        <v>52.37795502783314</v>
+        <v>53.43273666915255</v>
       </c>
       <c r="E47" t="n">
-        <v>52.47298252217111</v>
+        <v>53.43273666915255</v>
       </c>
       <c r="F47" t="n">
-        <v>8789100</v>
+        <v>9701900</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="B48" t="n">
-        <v>52.64402770996094</v>
+        <v>53.39472579956055</v>
       </c>
       <c r="C48" t="n">
-        <v>53.39472496847022</v>
+        <v>54.65856429071015</v>
       </c>
       <c r="D48" t="n">
-        <v>52.57751027724402</v>
+        <v>53.26169093205601</v>
       </c>
       <c r="E48" t="n">
-        <v>53.21417816894261</v>
+        <v>53.9173679575116</v>
       </c>
       <c r="F48" t="n">
-        <v>22059500</v>
+        <v>24300300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45898</v>
+        <v>45910</v>
       </c>
       <c r="B49" t="n">
-        <v>52.79607009887695</v>
+        <v>53.76532745361328</v>
       </c>
       <c r="C49" t="n">
-        <v>53.05263890273721</v>
+        <v>54.2119439898182</v>
       </c>
       <c r="D49" t="n">
-        <v>52.69154166490481</v>
+        <v>53.4802485954859</v>
       </c>
       <c r="E49" t="n">
-        <v>52.72955266360893</v>
+        <v>53.66079902229035</v>
       </c>
       <c r="F49" t="n">
-        <v>13885400</v>
+        <v>13463700</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45901</v>
+        <v>45911</v>
       </c>
       <c r="B50" t="n">
-        <v>52.83407592773438</v>
+        <v>54.18343734741211</v>
       </c>
       <c r="C50" t="n">
-        <v>52.83407592773438</v>
+        <v>54.42100064499375</v>
       </c>
       <c r="D50" t="n">
-        <v>52.0833786623851</v>
+        <v>53.50875845226303</v>
       </c>
       <c r="E50" t="n">
-        <v>52.39696033020376</v>
+        <v>53.64179331892023</v>
       </c>
       <c r="F50" t="n">
-        <v>7765400</v>
+        <v>14107200</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="B51" t="n">
-        <v>52.63452529907227</v>
+        <v>54.16443252563477</v>
       </c>
       <c r="C51" t="n">
-        <v>52.79607023150641</v>
+        <v>54.5730416925768</v>
       </c>
       <c r="D51" t="n">
-        <v>52.30193812189663</v>
+        <v>53.87935728995919</v>
       </c>
       <c r="E51" t="n">
-        <v>52.36845555733176</v>
+        <v>53.87935728995919</v>
       </c>
       <c r="F51" t="n">
-        <v>9578500</v>
+        <v>12303800</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="B52" t="n">
-        <v>52.83407592773438</v>
+        <v>54.63955688476562</v>
       </c>
       <c r="C52" t="n">
-        <v>53.04313278956565</v>
+        <v>54.68706881794066</v>
       </c>
       <c r="D52" t="n">
-        <v>52.49198782418536</v>
+        <v>54.14542480490332</v>
       </c>
       <c r="E52" t="n">
-        <v>52.63452362776539</v>
+        <v>54.62055138650998</v>
       </c>
       <c r="F52" t="n">
-        <v>11832100</v>
+        <v>12457500</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45904</v>
+        <v>45916</v>
       </c>
       <c r="B53" t="n">
-        <v>52.93860244750977</v>
+        <v>54.82960891723633</v>
       </c>
       <c r="C53" t="n">
-        <v>53.366217092669</v>
+        <v>55.17170064019209</v>
       </c>
       <c r="D53" t="n">
-        <v>52.78656208755628</v>
+        <v>54.34497776807294</v>
       </c>
       <c r="E53" t="n">
-        <v>53.07163730935306</v>
+        <v>54.89612634948571</v>
       </c>
       <c r="F53" t="n">
-        <v>8442100</v>
+        <v>15618500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="B54" t="n">
-        <v>53.42323684692383</v>
+        <v>54.92463302612305</v>
       </c>
       <c r="C54" t="n">
-        <v>53.85084789324807</v>
+        <v>55.13368988549875</v>
       </c>
       <c r="D54" t="n">
-        <v>53.23318547915287</v>
+        <v>54.50652293229983</v>
       </c>
       <c r="E54" t="n">
-        <v>53.4042313476539</v>
+        <v>54.67756879452937</v>
       </c>
       <c r="F54" t="n">
-        <v>14014700</v>
+        <v>23116700</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="B55" t="n">
-        <v>53.55627059936523</v>
+        <v>54.82010650634766</v>
       </c>
       <c r="C55" t="n">
-        <v>53.80333483486235</v>
+        <v>55.1907083040421</v>
       </c>
       <c r="D55" t="n">
-        <v>53.43273666915255</v>
+        <v>54.54453582975768</v>
       </c>
       <c r="E55" t="n">
-        <v>53.43273666915255</v>
+        <v>54.96264593814769</v>
       </c>
       <c r="F55" t="n">
-        <v>9701900</v>
+        <v>17700400</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45909</v>
+        <v>45919</v>
       </c>
       <c r="B56" t="n">
-        <v>53.39472579956055</v>
+        <v>55.03866195678711</v>
       </c>
       <c r="C56" t="n">
-        <v>54.65856429071015</v>
+        <v>55.29523074809968</v>
       </c>
       <c r="D56" t="n">
-        <v>53.26169093205601</v>
+        <v>54.68706929828981</v>
       </c>
       <c r="E56" t="n">
-        <v>53.9173679575116</v>
+        <v>55.08617751530765</v>
       </c>
       <c r="F56" t="n">
-        <v>24300300</v>
+        <v>25374600</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45910</v>
+        <v>45922</v>
       </c>
       <c r="B57" t="n">
-        <v>53.76532745361328</v>
+        <v>55.11468505859375</v>
       </c>
       <c r="C57" t="n">
-        <v>54.2119439898182</v>
+        <v>55.53279515751236</v>
       </c>
       <c r="D57" t="n">
-        <v>53.4802485954859</v>
+        <v>54.93413825734149</v>
       </c>
       <c r="E57" t="n">
-        <v>53.66079902229035</v>
+        <v>54.94363919427972</v>
       </c>
       <c r="F57" t="n">
-        <v>13463700</v>
+        <v>21947300</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="B58" t="n">
-        <v>54.18343734741211</v>
+        <v>54.80109786987305</v>
       </c>
       <c r="C58" t="n">
-        <v>54.42100064499375</v>
+        <v>55.48528130345996</v>
       </c>
       <c r="D58" t="n">
-        <v>53.50875845226303</v>
+        <v>54.79159693326351</v>
       </c>
       <c r="E58" t="n">
-        <v>53.64179331892023</v>
+        <v>55.11468315190976</v>
       </c>
       <c r="F58" t="n">
-        <v>14107200</v>
+        <v>17652400</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45912</v>
+        <v>45924</v>
       </c>
       <c r="B59" t="n">
-        <v>54.16443252563477</v>
+        <v>55.01015472412109</v>
       </c>
       <c r="C59" t="n">
-        <v>54.5730416925768</v>
+        <v>55.24771801356707</v>
       </c>
       <c r="D59" t="n">
-        <v>53.87935728995919</v>
+        <v>54.80109786943164</v>
       </c>
       <c r="E59" t="n">
-        <v>53.87935728995919</v>
+        <v>55.06717121856225</v>
       </c>
       <c r="F59" t="n">
-        <v>12303800</v>
+        <v>13005700</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="B60" t="n">
-        <v>54.63955688476562</v>
+        <v>55.31423568725586</v>
       </c>
       <c r="C60" t="n">
-        <v>54.68706881794066</v>
+        <v>55.63732190731674</v>
       </c>
       <c r="D60" t="n">
-        <v>54.14542480490332</v>
+        <v>55.15269438968949</v>
       </c>
       <c r="E60" t="n">
-        <v>54.62055138650998</v>
+        <v>55.29523018902544</v>
       </c>
       <c r="F60" t="n">
-        <v>12457500</v>
+        <v>13631100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45916</v>
+        <v>45926</v>
       </c>
       <c r="B61" t="n">
-        <v>54.82960891723633</v>
+        <v>54.24995422363281</v>
       </c>
       <c r="C61" t="n">
-        <v>55.17170064019209</v>
+        <v>55.05766797714445</v>
       </c>
       <c r="D61" t="n">
-        <v>54.34497776807294</v>
+        <v>53.72731569930597</v>
       </c>
       <c r="E61" t="n">
-        <v>54.89612634948571</v>
+        <v>54.86762024097339</v>
       </c>
       <c r="F61" t="n">
-        <v>15618500</v>
+        <v>29037000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45917</v>
+        <v>45929</v>
       </c>
       <c r="B62" t="n">
-        <v>54.92463302612305</v>
+        <v>54.43050003051758</v>
       </c>
       <c r="C62" t="n">
-        <v>55.13368988549875</v>
+        <v>54.87712017721827</v>
       </c>
       <c r="D62" t="n">
-        <v>54.50652293229983</v>
+        <v>54.28796423098818</v>
       </c>
       <c r="E62" t="n">
-        <v>54.67756879452937</v>
+        <v>54.6395568864078</v>
       </c>
       <c r="F62" t="n">
-        <v>23116700</v>
+        <v>15580200</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="B63" t="n">
-        <v>54.82010650634766</v>
+        <v>54.71557998657227</v>
       </c>
       <c r="C63" t="n">
-        <v>55.1907083040421</v>
+        <v>54.90562772312364</v>
       </c>
       <c r="D63" t="n">
-        <v>54.54453582975768</v>
+        <v>54.24995433219369</v>
       </c>
       <c r="E63" t="n">
-        <v>54.96264593814769</v>
+        <v>54.80109929306345</v>
       </c>
       <c r="F63" t="n">
-        <v>17700400</v>
+        <v>18280700</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="B64" t="n">
-        <v>55.03866195678711</v>
+        <v>55.40926361083984</v>
       </c>
       <c r="C64" t="n">
-        <v>55.29523074809968</v>
+        <v>55.75135170687278</v>
       </c>
       <c r="D64" t="n">
-        <v>54.68706929828981</v>
+        <v>54.88662146774475</v>
       </c>
       <c r="E64" t="n">
-        <v>55.08617751530765</v>
+        <v>54.88662146774475</v>
       </c>
       <c r="F64" t="n">
-        <v>25374600</v>
+        <v>18278300</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45922</v>
+        <v>45932</v>
       </c>
       <c r="B65" t="n">
-        <v>55.11468505859375</v>
+        <v>55.77986145019531</v>
       </c>
       <c r="C65" t="n">
-        <v>55.53279515751236</v>
+        <v>55.93190181143385</v>
       </c>
       <c r="D65" t="n">
-        <v>54.93413825734149</v>
+        <v>55.19070550351199</v>
       </c>
       <c r="E65" t="n">
-        <v>54.94363919427972</v>
+        <v>55.45677522944739</v>
       </c>
       <c r="F65" t="n">
-        <v>21947300</v>
+        <v>14824500</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="B66" t="n">
-        <v>54.80109786987305</v>
+        <v>55.67533493041992</v>
       </c>
       <c r="C66" t="n">
-        <v>55.48528130345996</v>
+        <v>56.17896796461038</v>
       </c>
       <c r="D66" t="n">
-        <v>54.79159693326351</v>
+        <v>55.58981199773397</v>
       </c>
       <c r="E66" t="n">
-        <v>55.11468315190976</v>
+        <v>55.77986336202812</v>
       </c>
       <c r="F66" t="n">
-        <v>17652400</v>
+        <v>19240200</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45924</v>
+        <v>45936</v>
       </c>
       <c r="B67" t="n">
-        <v>55.01015472412109</v>
+        <v>56.62558746337891</v>
       </c>
       <c r="C67" t="n">
-        <v>55.24771801356707</v>
+        <v>56.98668468881333</v>
       </c>
       <c r="D67" t="n">
-        <v>54.80109786943164</v>
+        <v>55.87488657692489</v>
       </c>
       <c r="E67" t="n">
-        <v>55.06717121856225</v>
+        <v>55.88439113873876</v>
       </c>
       <c r="F67" t="n">
-        <v>13005700</v>
+        <v>26102900</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="B68" t="n">
-        <v>55.31423568725586</v>
+        <v>55.82737350463867</v>
       </c>
       <c r="C68" t="n">
-        <v>55.63732190731674</v>
+        <v>56.65409274411046</v>
       </c>
       <c r="D68" t="n">
-        <v>55.15269438968949</v>
+        <v>55.82737350463867</v>
       </c>
       <c r="E68" t="n">
-        <v>55.29523018902544</v>
+        <v>56.54006337916598</v>
       </c>
       <c r="F68" t="n">
-        <v>13631100</v>
+        <v>26072300</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="B69" t="n">
-        <v>54.24995422363281</v>
+        <v>56.25498962402344</v>
       </c>
       <c r="C69" t="n">
-        <v>55.05766797714445</v>
+        <v>56.43553642531307</v>
       </c>
       <c r="D69" t="n">
-        <v>53.72731569930597</v>
+        <v>55.96040982988201</v>
       </c>
       <c r="E69" t="n">
-        <v>54.86762024097339</v>
+        <v>56.17896762878891</v>
       </c>
       <c r="F69" t="n">
-        <v>29037000</v>
+        <v>24609500</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45929</v>
+        <v>45939</v>
       </c>
       <c r="B70" t="n">
-        <v>54.43050003051758</v>
+        <v>56.16946792602539</v>
       </c>
       <c r="C70" t="n">
-        <v>54.87712017721827</v>
+        <v>57.37628993992843</v>
       </c>
       <c r="D70" t="n">
-        <v>54.28796423098818</v>
+        <v>56.16946792602539</v>
       </c>
       <c r="E70" t="n">
-        <v>54.6395568864078</v>
+        <v>56.88215783483147</v>
       </c>
       <c r="F70" t="n">
-        <v>15580200</v>
+        <v>18184600</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="B71" t="n">
-        <v>54.71557998657227</v>
+        <v>55.94140243530273</v>
       </c>
       <c r="C71" t="n">
-        <v>54.90562772312364</v>
+        <v>56.82513816285029</v>
       </c>
       <c r="D71" t="n">
-        <v>54.24995433219369</v>
+        <v>55.94140243530273</v>
       </c>
       <c r="E71" t="n">
-        <v>54.80109929306345</v>
+        <v>56.60658037134998</v>
       </c>
       <c r="F71" t="n">
-        <v>18280700</v>
+        <v>22970400</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="B72" t="n">
-        <v>55.40926361083984</v>
+        <v>56.77762985229492</v>
       </c>
       <c r="C72" t="n">
-        <v>55.75135170687278</v>
+        <v>57.07220965524756</v>
       </c>
       <c r="D72" t="n">
-        <v>54.88662146774475</v>
+        <v>56.58757848345219</v>
       </c>
       <c r="E72" t="n">
-        <v>54.88662146774475</v>
+        <v>56.70160785478649</v>
       </c>
       <c r="F72" t="n">
-        <v>18278300</v>
+        <v>23294500</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="B73" t="n">
-        <v>55.77986145019531</v>
+        <v>56.77762985229492</v>
       </c>
       <c r="C73" t="n">
-        <v>55.93190181143385</v>
+        <v>57.13872709060326</v>
       </c>
       <c r="D73" t="n">
-        <v>55.19070550351199</v>
+        <v>56.2739968060508</v>
       </c>
       <c r="E73" t="n">
-        <v>55.45677522944739</v>
+        <v>56.35001517863088</v>
       </c>
       <c r="F73" t="n">
-        <v>14824500</v>
+        <v>19329000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45933</v>
+        <v>45945</v>
       </c>
       <c r="B74" t="n">
-        <v>55.67533493041992</v>
+        <v>57.8324089050293</v>
       </c>
       <c r="C74" t="n">
-        <v>56.17896796461038</v>
+        <v>57.94643827123581</v>
       </c>
       <c r="D74" t="n">
-        <v>55.58981199773397</v>
+        <v>56.50205300788323</v>
       </c>
       <c r="E74" t="n">
-        <v>55.77986336202812</v>
+        <v>56.53056306813101</v>
       </c>
       <c r="F74" t="n">
-        <v>19240200</v>
+        <v>45104600</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="B75" t="n">
-        <v>56.62558746337891</v>
+        <v>57.30026626586914</v>
       </c>
       <c r="C75" t="n">
-        <v>56.98668468881333</v>
+        <v>57.89892678672364</v>
       </c>
       <c r="D75" t="n">
-        <v>55.87488657692489</v>
+        <v>57.0817084685571</v>
       </c>
       <c r="E75" t="n">
-        <v>55.88439113873876</v>
+        <v>57.59484605786096</v>
       </c>
       <c r="F75" t="n">
-        <v>26102900</v>
+        <v>21358500</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c r="B76" t="n">
-        <v>55.82737350463867</v>
+        <v>57.13872528076172</v>
       </c>
       <c r="C76" t="n">
-        <v>56.65409274411046</v>
+        <v>57.30026658295786</v>
       </c>
       <c r="D76" t="n">
-        <v>55.82737350463867</v>
+        <v>56.82513998836463</v>
       </c>
       <c r="E76" t="n">
-        <v>56.54006337916598</v>
+        <v>56.92016748224022</v>
       </c>
       <c r="F76" t="n">
-        <v>26072300</v>
+        <v>17325300</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45938</v>
+        <v>45950</v>
       </c>
       <c r="B77" t="n">
-        <v>56.25498962402344</v>
+        <v>57.87042236328125</v>
       </c>
       <c r="C77" t="n">
-        <v>56.43553642531307</v>
+        <v>58.29803341097386</v>
       </c>
       <c r="D77" t="n">
-        <v>55.96040982988201</v>
+        <v>57.14822788842621</v>
       </c>
       <c r="E77" t="n">
-        <v>56.17896762878891</v>
+        <v>57.14822788842621</v>
       </c>
       <c r="F77" t="n">
-        <v>24609500</v>
+        <v>17798400</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="B78" t="n">
-        <v>56.16946792602539</v>
+        <v>57.77539443969727</v>
       </c>
       <c r="C78" t="n">
-        <v>57.37628993992843</v>
+        <v>58.01295774218363</v>
       </c>
       <c r="D78" t="n">
-        <v>56.16946792602539</v>
+        <v>57.55683663640121</v>
       </c>
       <c r="E78" t="n">
-        <v>56.88215783483147</v>
+        <v>57.63285863316244</v>
       </c>
       <c r="F78" t="n">
-        <v>18184600</v>
+        <v>13432700</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45940</v>
+        <v>45952</v>
       </c>
       <c r="B79" t="n">
-        <v>55.94140243530273</v>
+        <v>58.80167007446289</v>
       </c>
       <c r="C79" t="n">
-        <v>56.82513816285029</v>
+        <v>59.14376181252211</v>
       </c>
       <c r="D79" t="n">
-        <v>55.94140243530273</v>
+        <v>58.13649209767312</v>
       </c>
       <c r="E79" t="n">
-        <v>56.60658037134998</v>
+        <v>58.16499853420193</v>
       </c>
       <c r="F79" t="n">
-        <v>22970400</v>
+        <v>25267300</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45943</v>
+        <v>45953</v>
       </c>
       <c r="B80" t="n">
-        <v>56.77762985229492</v>
+        <v>58.6876335144043</v>
       </c>
       <c r="C80" t="n">
-        <v>57.07220965524756</v>
+        <v>59.42883344349582</v>
       </c>
       <c r="D80" t="n">
-        <v>56.58757848345219</v>
+        <v>58.60211058508328</v>
       </c>
       <c r="E80" t="n">
-        <v>56.70160785478649</v>
+        <v>59.12475272256067</v>
       </c>
       <c r="F80" t="n">
-        <v>23294500</v>
+        <v>11217700</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="B81" t="n">
-        <v>56.77762985229492</v>
+        <v>58.65913009643555</v>
       </c>
       <c r="C81" t="n">
-        <v>57.13872709060326</v>
+        <v>59.03923282961716</v>
       </c>
       <c r="D81" t="n">
-        <v>56.2739968060508</v>
+        <v>58.27903098818225</v>
       </c>
       <c r="E81" t="n">
-        <v>56.35001517863088</v>
+        <v>58.90619796048208</v>
       </c>
       <c r="F81" t="n">
-        <v>19329000</v>
+        <v>11127600</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45945</v>
+        <v>45957</v>
       </c>
       <c r="B82" t="n">
-        <v>57.8324089050293</v>
+        <v>58.59261322021484</v>
       </c>
       <c r="C82" t="n">
-        <v>57.94643827123581</v>
+        <v>59.06773982875533</v>
       </c>
       <c r="D82" t="n">
-        <v>56.50205300788323</v>
+        <v>58.34554897874227</v>
       </c>
       <c r="E82" t="n">
-        <v>56.53056306813101</v>
+        <v>58.97271595701857</v>
       </c>
       <c r="F82" t="n">
-        <v>45104600</v>
+        <v>12018100</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45946</v>
+        <v>45958</v>
       </c>
       <c r="B83" t="n">
-        <v>57.30026626586914</v>
+        <v>59.10574722290039</v>
       </c>
       <c r="C83" t="n">
-        <v>57.89892678672364</v>
+        <v>59.42883344200187</v>
       </c>
       <c r="D83" t="n">
-        <v>57.0817084685571</v>
+        <v>58.51659127921938</v>
       </c>
       <c r="E83" t="n">
-        <v>57.59484605786096</v>
+        <v>58.59260964698719</v>
       </c>
       <c r="F83" t="n">
-        <v>21358500</v>
+        <v>15797400</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45947</v>
+        <v>45959</v>
       </c>
       <c r="B84" t="n">
-        <v>57.13872528076172</v>
+        <v>60.17953491210938</v>
       </c>
       <c r="C84" t="n">
-        <v>57.30026658295786</v>
+        <v>60.52162300789247</v>
       </c>
       <c r="D84" t="n">
-        <v>56.82513998836463</v>
+        <v>59.59037533758303</v>
       </c>
       <c r="E84" t="n">
-        <v>56.92016748224022</v>
+        <v>59.69490376612571</v>
       </c>
       <c r="F84" t="n">
-        <v>17325300</v>
+        <v>30844900</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45950</v>
+        <v>45960</v>
       </c>
       <c r="B85" t="n">
-        <v>57.87042236328125</v>
+        <v>60.63565826416016</v>
       </c>
       <c r="C85" t="n">
-        <v>58.29803341097386</v>
+        <v>60.81620506798154</v>
       </c>
       <c r="D85" t="n">
-        <v>57.14822788842621</v>
+        <v>59.79943442949548</v>
       </c>
       <c r="E85" t="n">
-        <v>57.14822788842621</v>
+        <v>59.97048029624344</v>
       </c>
       <c r="F85" t="n">
-        <v>17798400</v>
+        <v>25586000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45951</v>
+        <v>45961</v>
       </c>
       <c r="B86" t="n">
-        <v>57.77539443969727</v>
+        <v>62.01352691650391</v>
       </c>
       <c r="C86" t="n">
-        <v>58.01295774218363</v>
+        <v>62.28910121917285</v>
       </c>
       <c r="D86" t="n">
-        <v>57.55683663640121</v>
+        <v>60.69267190110292</v>
       </c>
       <c r="E86" t="n">
-        <v>57.63285863316244</v>
+        <v>61.08227557473102</v>
       </c>
       <c r="F86" t="n">
-        <v>13432700</v>
+        <v>38988400</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="B87" t="n">
-        <v>58.80167007446289</v>
+        <v>62.09904479980469</v>
       </c>
       <c r="C87" t="n">
-        <v>59.14376181252211</v>
+        <v>62.13705579756086</v>
       </c>
       <c r="D87" t="n">
-        <v>58.13649209767312</v>
+        <v>61.43387046371297</v>
       </c>
       <c r="E87" t="n">
-        <v>58.16499853420193</v>
+        <v>61.861481501221</v>
       </c>
       <c r="F87" t="n">
-        <v>25267300</v>
+        <v>16985400</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45953</v>
+        <v>45965</v>
       </c>
       <c r="B88" t="n">
-        <v>58.6876335144043</v>
+        <v>61.40536499023438</v>
       </c>
       <c r="C88" t="n">
-        <v>59.42883344349582</v>
+        <v>61.7759631618446</v>
       </c>
       <c r="D88" t="n">
-        <v>58.60211058508328</v>
+        <v>60.84471182686465</v>
       </c>
       <c r="E88" t="n">
-        <v>59.12475272256067</v>
+        <v>61.623919168437</v>
       </c>
       <c r="F88" t="n">
-        <v>11217700</v>
+        <v>22055700</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45954</v>
+        <v>45966</v>
       </c>
       <c r="B89" t="n">
-        <v>58.65913009643555</v>
+        <v>62.46014404296875</v>
       </c>
       <c r="C89" t="n">
-        <v>59.03923282961716</v>
+        <v>62.87825050779235</v>
       </c>
       <c r="D89" t="n">
-        <v>58.27903098818225</v>
+        <v>61.29132945413907</v>
       </c>
       <c r="E89" t="n">
-        <v>58.90619796048208</v>
+        <v>61.40536244446715</v>
       </c>
       <c r="F89" t="n">
-        <v>11127600</v>
+        <v>22505400</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45957</v>
+        <v>45967</v>
       </c>
       <c r="B90" t="n">
-        <v>58.59261322021484</v>
+        <v>62.24158477783203</v>
       </c>
       <c r="C90" t="n">
-        <v>59.06773982875533</v>
+        <v>62.76422693926791</v>
       </c>
       <c r="D90" t="n">
-        <v>58.34554897874227</v>
+        <v>62.01352603914027</v>
       </c>
       <c r="E90" t="n">
-        <v>58.97271595701857</v>
+        <v>62.48865264049777</v>
       </c>
       <c r="F90" t="n">
-        <v>12018100</v>
+        <v>15939100</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="B91" t="n">
-        <v>59.10574722290039</v>
+        <v>61.55739974975586</v>
       </c>
       <c r="C91" t="n">
-        <v>59.42883344200187</v>
+        <v>61.63342174400943</v>
       </c>
       <c r="D91" t="n">
-        <v>58.51659127921938</v>
+        <v>60.83520530405978</v>
       </c>
       <c r="E91" t="n">
-        <v>58.59260964698719</v>
+        <v>61.62391718226363</v>
       </c>
       <c r="F91" t="n">
-        <v>15797400</v>
+        <v>20800300</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45959</v>
+        <v>45971</v>
       </c>
       <c r="B92" t="n">
-        <v>60.17953491210938</v>
+        <v>61.96601104736328</v>
       </c>
       <c r="C92" t="n">
-        <v>60.52162300789247</v>
+        <v>62.27959634710076</v>
       </c>
       <c r="D92" t="n">
-        <v>59.59037533758303</v>
+        <v>61.68093943384829</v>
       </c>
       <c r="E92" t="n">
-        <v>59.69490376612571</v>
+        <v>61.82347161567746</v>
       </c>
       <c r="F92" t="n">
-        <v>30844900</v>
+        <v>12689400</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45960</v>
+        <v>45972</v>
       </c>
       <c r="B93" t="n">
-        <v>60.63565826416016</v>
+        <v>61.80447006225586</v>
       </c>
       <c r="C93" t="n">
-        <v>60.81620506798154</v>
+        <v>62.39362966634955</v>
       </c>
       <c r="D93" t="n">
-        <v>59.79943442949548</v>
+        <v>61.53840032165119</v>
       </c>
       <c r="E93" t="n">
-        <v>59.97048029624344</v>
+        <v>61.96601136907203</v>
       </c>
       <c r="F93" t="n">
-        <v>25586000</v>
+        <v>25496500</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="B94" t="n">
-        <v>62.01352691650391</v>
+        <v>62.48865127563477</v>
       </c>
       <c r="C94" t="n">
-        <v>62.28910121917285</v>
+        <v>62.66919445030475</v>
       </c>
       <c r="D94" t="n">
-        <v>60.69267190110292</v>
+        <v>62.01352468465488</v>
       </c>
       <c r="E94" t="n">
-        <v>61.08227557473102</v>
+        <v>62.01352468465488</v>
       </c>
       <c r="F94" t="n">
-        <v>38988400</v>
+        <v>26550300</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45964</v>
+        <v>45974</v>
       </c>
       <c r="B95" t="n">
-        <v>62.09904479980469</v>
+        <v>62.40312576293945</v>
       </c>
       <c r="C95" t="n">
-        <v>62.13705579756086</v>
+        <v>63.14432209728654</v>
       </c>
       <c r="D95" t="n">
-        <v>61.43387046371297</v>
+        <v>62.06103403172441</v>
       </c>
       <c r="E95" t="n">
-        <v>61.861481501221</v>
+        <v>62.48865232067149</v>
       </c>
       <c r="F95" t="n">
-        <v>16985400</v>
+        <v>19058500</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="B96" t="n">
-        <v>61.40536499023438</v>
+        <v>62.02302169799805</v>
       </c>
       <c r="C96" t="n">
-        <v>61.7759631618446</v>
+        <v>62.27959411581164</v>
       </c>
       <c r="D96" t="n">
-        <v>60.84471182686465</v>
+        <v>61.39585837084911</v>
       </c>
       <c r="E96" t="n">
-        <v>61.623919168437</v>
+        <v>61.62391710346178</v>
       </c>
       <c r="F96" t="n">
-        <v>22055700</v>
+        <v>16374400</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="B97" t="n">
-        <v>62.46014404296875</v>
+        <v>61.97551345825195</v>
       </c>
       <c r="C97" t="n">
-        <v>62.87825050779235</v>
+        <v>62.49814835648363</v>
       </c>
       <c r="D97" t="n">
-        <v>61.29132945413907</v>
+        <v>61.68093729288761</v>
       </c>
       <c r="E97" t="n">
-        <v>61.40536244446715</v>
+        <v>62.33660705611328</v>
       </c>
       <c r="F97" t="n">
-        <v>22505400</v>
+        <v>20150800</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="B98" t="n">
-        <v>62.24158477783203</v>
+        <v>61.78545761108398</v>
       </c>
       <c r="C98" t="n">
-        <v>62.76422693926791</v>
+        <v>62.04203002560634</v>
       </c>
       <c r="D98" t="n">
-        <v>62.01352603914027</v>
+        <v>61.10128142202241</v>
       </c>
       <c r="E98" t="n">
-        <v>62.48865264049777</v>
+        <v>61.24381359691672</v>
       </c>
       <c r="F98" t="n">
-        <v>15939100</v>
+        <v>22468700</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="B99" t="n">
-        <v>61.55739974975586</v>
+        <v>61.71894073486328</v>
       </c>
       <c r="C99" t="n">
-        <v>61.63342174400943</v>
+        <v>62.01352414862689</v>
       </c>
       <c r="D99" t="n">
-        <v>60.83520530405978</v>
+        <v>61.48137744142677</v>
       </c>
       <c r="E99" t="n">
-        <v>61.62391718226363</v>
+        <v>61.78545816703124</v>
       </c>
       <c r="F99" t="n">
-        <v>20800300</v>
+        <v>16523800</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>61.96601104736328</v>
+        <v>61.91850280761719</v>
       </c>
       <c r="C100" t="n">
-        <v>62.27959634710076</v>
+        <v>62.02302399112606</v>
       </c>
       <c r="D100" t="n">
-        <v>61.68093943384829</v>
+        <v>60.93973590884384</v>
       </c>
       <c r="E100" t="n">
-        <v>61.82347161567746</v>
+        <v>61.33884776799255</v>
       </c>
       <c r="F100" t="n">
-        <v>12689400</v>
+        <v>20272600</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>61.80447006225586</v>
+        <v>61.85197830200195</v>
       </c>
       <c r="C101" t="n">
-        <v>62.39362966634955</v>
+        <v>62.26058747456238</v>
       </c>
       <c r="D101" t="n">
-        <v>61.53840032165119</v>
+        <v>61.55740212522235</v>
       </c>
       <c r="E101" t="n">
-        <v>61.96601136907203</v>
+        <v>61.77596355467142</v>
       </c>
       <c r="F101" t="n">
-        <v>25496500</v>
+        <v>20462800</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>62.48865127563477</v>
+        <v>62.33660888671875</v>
       </c>
       <c r="C102" t="n">
-        <v>62.66919445030475</v>
+        <v>62.63119231059036</v>
       </c>
       <c r="D102" t="n">
-        <v>62.01352468465488</v>
+        <v>61.91850240582638</v>
       </c>
       <c r="E102" t="n">
-        <v>62.01352468465488</v>
+        <v>61.91850240582638</v>
       </c>
       <c r="F102" t="n">
-        <v>26550300</v>
+        <v>18275300</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45974</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>62.40312576293945</v>
+        <v>63.26786041259766</v>
       </c>
       <c r="C103" t="n">
-        <v>63.14432209728654</v>
+        <v>63.5624365875146</v>
       </c>
       <c r="D103" t="n">
-        <v>62.06103403172441</v>
+        <v>62.64068981455387</v>
       </c>
       <c r="E103" t="n">
-        <v>62.48865232067149</v>
+        <v>62.7072072492079</v>
       </c>
       <c r="F103" t="n">
-        <v>19058500</v>
+        <v>33408500</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45975</v>
+        <v>45988</v>
       </c>
       <c r="B104" t="n">
-        <v>62.02302169799805</v>
+        <v>63.03029632568359</v>
       </c>
       <c r="C104" t="n">
-        <v>62.27959411581164</v>
+        <v>63.33437705886783</v>
       </c>
       <c r="D104" t="n">
-        <v>61.39585837084911</v>
+        <v>62.84974589821726</v>
       </c>
       <c r="E104" t="n">
-        <v>61.62391710346178</v>
+        <v>63.1918376292816</v>
       </c>
       <c r="F104" t="n">
-        <v>16374400</v>
+        <v>9739100</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45978</v>
+        <v>45989</v>
       </c>
       <c r="B105" t="n">
-        <v>61.97551345825195</v>
+        <v>64.04706573486328</v>
       </c>
       <c r="C105" t="n">
-        <v>62.49814835648363</v>
+        <v>64.43666576845139</v>
       </c>
       <c r="D105" t="n">
-        <v>61.68093729288761</v>
+        <v>63.70497401032638</v>
       </c>
       <c r="E105" t="n">
-        <v>62.33660705611328</v>
+        <v>64.33213733873976</v>
       </c>
       <c r="F105" t="n">
-        <v>20150800</v>
+        <v>46007200</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45979</v>
+        <v>45992</v>
       </c>
       <c r="B106" t="n">
-        <v>61.78545761108398</v>
+        <v>64.54119110107422</v>
       </c>
       <c r="C106" t="n">
-        <v>62.04203002560634</v>
+        <v>64.74074338916891</v>
       </c>
       <c r="D106" t="n">
-        <v>61.10128142202241</v>
+        <v>64.14208652488483</v>
       </c>
       <c r="E106" t="n">
-        <v>61.24381359691672</v>
+        <v>64.42716536493786</v>
       </c>
       <c r="F106" t="n">
-        <v>22468700</v>
+        <v>15657000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45980</v>
+        <v>45993</v>
       </c>
       <c r="B107" t="n">
-        <v>61.71894073486328</v>
+        <v>65.07334136962891</v>
       </c>
       <c r="C107" t="n">
-        <v>62.01352414862689</v>
+        <v>65.30140010431755</v>
       </c>
       <c r="D107" t="n">
-        <v>61.48137744142677</v>
+        <v>64.38915791570652</v>
       </c>
       <c r="E107" t="n">
-        <v>61.78545816703124</v>
+        <v>64.71224051902739</v>
       </c>
       <c r="F107" t="n">
-        <v>16523800</v>
+        <v>22567200</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="B108" t="n">
-        <v>61.91850280761719</v>
+        <v>67.17340087890625</v>
       </c>
       <c r="C108" t="n">
-        <v>62.02302399112606</v>
+        <v>67.56300092011637</v>
       </c>
       <c r="D108" t="n">
-        <v>60.93973590884384</v>
+        <v>65.39642478890073</v>
       </c>
       <c r="E108" t="n">
-        <v>61.33884776799255</v>
+        <v>65.43443578679917</v>
       </c>
       <c r="F108" t="n">
-        <v>20272600</v>
+        <v>42361200</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B109" t="n">
-        <v>61.85197830200195</v>
+        <v>68.34220886230469</v>
       </c>
       <c r="C109" t="n">
-        <v>62.26058747456238</v>
+        <v>68.78882902927656</v>
       </c>
       <c r="D109" t="n">
-        <v>61.55740212522235</v>
+        <v>67.17340147838691</v>
       </c>
       <c r="E109" t="n">
-        <v>61.77596355467142</v>
+        <v>67.18289879055385</v>
       </c>
       <c r="F109" t="n">
-        <v>20462800</v>
+        <v>38019900</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="B110" t="n">
-        <v>62.33660888671875</v>
+        <v>66.72678375244141</v>
       </c>
       <c r="C110" t="n">
-        <v>62.63119231059036</v>
+        <v>68.73181867122375</v>
       </c>
       <c r="D110" t="n">
-        <v>61.91850240582638</v>
+        <v>66.4417048801583</v>
       </c>
       <c r="E110" t="n">
-        <v>61.91850240582638</v>
+        <v>68.38022236205551</v>
       </c>
       <c r="F110" t="n">
-        <v>18275300</v>
+        <v>40196800</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45987</v>
+        <v>45999</v>
       </c>
       <c r="B111" t="n">
-        <v>63.26786041259766</v>
+        <v>66.27065277099609</v>
       </c>
       <c r="C111" t="n">
-        <v>63.5624365875146</v>
+        <v>67.33493891087078</v>
       </c>
       <c r="D111" t="n">
-        <v>62.64068981455387</v>
+        <v>66.03308948306608</v>
       </c>
       <c r="E111" t="n">
-        <v>62.7072072492079</v>
+        <v>66.91682520415998</v>
       </c>
       <c r="F111" t="n">
-        <v>33408500</v>
+        <v>20860900</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45988</v>
+        <v>46000</v>
       </c>
       <c r="B112" t="n">
-        <v>63.03029632568359</v>
+        <v>66.30867004394531</v>
       </c>
       <c r="C112" t="n">
-        <v>63.33437705886783</v>
+        <v>66.92633610100395</v>
       </c>
       <c r="D112" t="n">
-        <v>62.84974589821726</v>
+        <v>65.4724498012218</v>
       </c>
       <c r="E112" t="n">
-        <v>63.1918376292816</v>
+        <v>65.66249754961359</v>
       </c>
       <c r="F112" t="n">
-        <v>9739100</v>
+        <v>23081300</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="B113" t="n">
-        <v>64.04706573486328</v>
+        <v>67.52498626708984</v>
       </c>
       <c r="C113" t="n">
-        <v>64.43666576845139</v>
+        <v>67.80056054954433</v>
       </c>
       <c r="D113" t="n">
-        <v>63.70497401032638</v>
+        <v>66.75528353841582</v>
       </c>
       <c r="E113" t="n">
-        <v>64.33213733873976</v>
+        <v>66.75528353841582</v>
       </c>
       <c r="F113" t="n">
-        <v>46007200</v>
+        <v>24454800</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="B114" t="n">
-        <v>64.54119110107422</v>
+        <v>68.41822814941406</v>
       </c>
       <c r="C114" t="n">
-        <v>64.74074338916891</v>
+        <v>68.76982443179682</v>
       </c>
       <c r="D114" t="n">
-        <v>64.14208652488483</v>
+        <v>66.96434196121602</v>
       </c>
       <c r="E114" t="n">
-        <v>64.42716536493786</v>
+        <v>67.22090712683953</v>
       </c>
       <c r="F114" t="n">
-        <v>15657000</v>
+        <v>25687700</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="B115" t="n">
-        <v>65.07334136962891</v>
+        <v>68.61000061035156</v>
       </c>
       <c r="C115" t="n">
-        <v>65.30140010431755</v>
+        <v>68.98000335693359</v>
       </c>
       <c r="D115" t="n">
-        <v>64.38915791570652</v>
+        <v>67.72000122070312</v>
       </c>
       <c r="E115" t="n">
-        <v>64.71224051902739</v>
+        <v>67.75</v>
       </c>
       <c r="F115" t="n">
-        <v>22567200</v>
+        <v>36483700</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="B116" t="n">
-        <v>67.17340087890625</v>
+        <v>69.02999877929688</v>
       </c>
       <c r="C116" t="n">
-        <v>67.56300092011637</v>
+        <v>69.38999938964844</v>
       </c>
       <c r="D116" t="n">
-        <v>65.39642478890073</v>
+        <v>68.5</v>
       </c>
       <c r="E116" t="n">
-        <v>65.43443578679917</v>
+        <v>68.65000152587891</v>
       </c>
       <c r="F116" t="n">
-        <v>42361200</v>
+        <v>16841700</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="B117" t="n">
-        <v>68.34220886230469</v>
+        <v>69.29000091552734</v>
       </c>
       <c r="C117" t="n">
-        <v>68.78882902927656</v>
+        <v>70.02999877929688</v>
       </c>
       <c r="D117" t="n">
-        <v>67.17340147838691</v>
+        <v>69.26000213623047</v>
       </c>
       <c r="E117" t="n">
-        <v>67.18289879055385</v>
+        <v>69.33000183105469</v>
       </c>
       <c r="F117" t="n">
-        <v>38019900</v>
+        <v>21953000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="B118" t="n">
-        <v>66.72678375244141</v>
+        <v>70.16999816894531</v>
       </c>
       <c r="C118" t="n">
-        <v>68.73181867122375</v>
+        <v>70.76999664306641</v>
       </c>
       <c r="D118" t="n">
-        <v>66.4417048801583</v>
+        <v>69.44000244140625</v>
       </c>
       <c r="E118" t="n">
-        <v>68.38022236205551</v>
+        <v>69.63999938964844</v>
       </c>
       <c r="F118" t="n">
-        <v>40196800</v>
+        <v>29375000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="B119" t="n">
-        <v>66.27065277099609</v>
+        <v>70.34999847412109</v>
       </c>
       <c r="C119" t="n">
-        <v>67.33493891087078</v>
+        <v>71.12000274658203</v>
       </c>
       <c r="D119" t="n">
-        <v>66.03308948306608</v>
+        <v>70.30999755859375</v>
       </c>
       <c r="E119" t="n">
-        <v>66.91682520415998</v>
+        <v>70.59999847412109</v>
       </c>
       <c r="F119" t="n">
-        <v>20860900</v>
+        <v>18430200</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="B120" t="n">
-        <v>66.30867004394531</v>
+        <v>70.84999847412109</v>
       </c>
       <c r="C120" t="n">
-        <v>66.92633610100395</v>
+        <v>70.93000030517578</v>
       </c>
       <c r="D120" t="n">
-        <v>65.4724498012218</v>
+        <v>70.37999725341797</v>
       </c>
       <c r="E120" t="n">
-        <v>65.66249754961359</v>
+        <v>70.5</v>
       </c>
       <c r="F120" t="n">
-        <v>23081300</v>
+        <v>37147100</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="B121" t="n">
-        <v>67.52498626708984</v>
+        <v>72.91999816894531</v>
       </c>
       <c r="C121" t="n">
-        <v>67.80056054954433</v>
+        <v>73.37000274658203</v>
       </c>
       <c r="D121" t="n">
-        <v>66.75528353841582</v>
+        <v>70.80999755859375</v>
       </c>
       <c r="E121" t="n">
-        <v>66.75528353841582</v>
+        <v>71.02999877929688</v>
       </c>
       <c r="F121" t="n">
-        <v>24454800</v>
+        <v>27853000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="B122" t="n">
-        <v>68.41822814941406</v>
+        <v>72.90000152587891</v>
       </c>
       <c r="C122" t="n">
-        <v>68.76982443179682</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="D122" t="n">
-        <v>66.96434196121602</v>
+        <v>72.58000183105469</v>
       </c>
       <c r="E122" t="n">
-        <v>67.22090712683953</v>
+        <v>73.23000335693359</v>
       </c>
       <c r="F122" t="n">
-        <v>25687700</v>
+        <v>17140900</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46003</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>68.61000061035156</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C123" t="n">
-        <v>68.98000335693359</v>
+        <v>73.34999847412109</v>
       </c>
       <c r="D123" t="n">
-        <v>67.72000122070312</v>
+        <v>72.62000274658203</v>
       </c>
       <c r="E123" t="n">
-        <v>67.75</v>
+        <v>72.86000061035156</v>
       </c>
       <c r="F123" t="n">
-        <v>36483700</v>
+        <v>16368800</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>69.02999877929688</v>
+        <v>72.12000274658203</v>
       </c>
       <c r="C124" t="n">
-        <v>69.38999938964844</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="D124" t="n">
-        <v>68.5</v>
+        <v>71.69999694824219</v>
       </c>
       <c r="E124" t="n">
-        <v>68.65000152587891</v>
+        <v>73.19000244140625</v>
       </c>
       <c r="F124" t="n">
-        <v>16841700</v>
+        <v>19963700</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>69.29000091552734</v>
+        <v>71.95999908447266</v>
       </c>
       <c r="C125" t="n">
-        <v>70.02999877929688</v>
+        <v>72.83999633789062</v>
       </c>
       <c r="D125" t="n">
-        <v>69.26000213623047</v>
+        <v>71.91000366210938</v>
       </c>
       <c r="E125" t="n">
-        <v>69.33000183105469</v>
+        <v>72.5</v>
       </c>
       <c r="F125" t="n">
-        <v>21953000</v>
+        <v>17085400</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="B126" t="n">
-        <v>70.16999816894531</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="C126" t="n">
-        <v>70.76999664306641</v>
+        <v>72.55000305175781</v>
       </c>
       <c r="D126" t="n">
-        <v>69.44000244140625</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="E126" t="n">
-        <v>69.63999938964844</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="F126" t="n">
-        <v>29375000</v>
+        <v>28418900</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46009</v>
+        <v>46027</v>
       </c>
       <c r="B127" t="n">
-        <v>70.34999847412109</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C127" t="n">
-        <v>71.12000274658203</v>
+        <v>73.5</v>
       </c>
       <c r="D127" t="n">
-        <v>70.30999755859375</v>
+        <v>72.30000305175781</v>
       </c>
       <c r="E127" t="n">
-        <v>70.59999847412109</v>
+        <v>72.40000152587891</v>
       </c>
       <c r="F127" t="n">
-        <v>18430200</v>
+        <v>24958100</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="B128" t="n">
-        <v>70.84999847412109</v>
+        <v>75.87000274658203</v>
       </c>
       <c r="C128" t="n">
-        <v>70.93000030517578</v>
+        <v>75.98999786376953</v>
       </c>
       <c r="D128" t="n">
-        <v>70.37999725341797</v>
+        <v>72.87999725341797</v>
       </c>
       <c r="E128" t="n">
-        <v>70.5</v>
+        <v>73.44999694824219</v>
       </c>
       <c r="F128" t="n">
-        <v>37147100</v>
+        <v>39536600</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="B129" t="n">
-        <v>72.91999816894531</v>
+        <v>76.31999969482422</v>
       </c>
       <c r="C129" t="n">
-        <v>73.37000274658203</v>
+        <v>77.33999633789062</v>
       </c>
       <c r="D129" t="n">
-        <v>70.80999755859375</v>
+        <v>75.62000274658203</v>
       </c>
       <c r="E129" t="n">
-        <v>71.02999877929688</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="F129" t="n">
-        <v>27853000</v>
+        <v>41501600</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="B130" t="n">
-        <v>72.90000152587891</v>
+        <v>75.58000183105469</v>
       </c>
       <c r="C130" t="n">
-        <v>73.52999877929688</v>
+        <v>75.80000305175781</v>
       </c>
       <c r="D130" t="n">
-        <v>72.58000183105469</v>
+        <v>74.19000244140625</v>
       </c>
       <c r="E130" t="n">
-        <v>73.23000335693359</v>
+        <v>75.80000305175781</v>
       </c>
       <c r="F130" t="n">
-        <v>17140900</v>
+        <v>31894900</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46017</v>
+        <v>46031</v>
       </c>
       <c r="B131" t="n">
-        <v>73.12000274658203</v>
+        <v>74.72000122070312</v>
       </c>
       <c r="C131" t="n">
-        <v>73.34999847412109</v>
+        <v>75.70999908447266</v>
       </c>
       <c r="D131" t="n">
-        <v>72.62000274658203</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="E131" t="n">
-        <v>72.86000061035156</v>
+        <v>74.90000152587891</v>
       </c>
       <c r="F131" t="n">
-        <v>16368800</v>
+        <v>24801200</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46020</v>
+        <v>46034</v>
       </c>
       <c r="B132" t="n">
-        <v>72.12000274658203</v>
+        <v>74.73999786376953</v>
       </c>
       <c r="C132" t="n">
-        <v>73.73999786376953</v>
+        <v>75.47000122070312</v>
       </c>
       <c r="D132" t="n">
-        <v>71.69999694824219</v>
+        <v>74.51000213623047</v>
       </c>
       <c r="E132" t="n">
-        <v>73.19000244140625</v>
+        <v>75</v>
       </c>
       <c r="F132" t="n">
-        <v>19963700</v>
+        <v>13129800</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46021</v>
+        <v>46035</v>
       </c>
       <c r="B133" t="n">
-        <v>71.95999908447266</v>
+        <v>75.34999847412109</v>
       </c>
       <c r="C133" t="n">
-        <v>72.83999633789062</v>
+        <v>76.05000305175781</v>
       </c>
       <c r="D133" t="n">
-        <v>71.91000366210938</v>
+        <v>74.27999877929688</v>
       </c>
       <c r="E133" t="n">
-        <v>72.5</v>
+        <v>74.47000122070312</v>
       </c>
       <c r="F133" t="n">
-        <v>17085400</v>
+        <v>24539200</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46024</v>
+        <v>46036</v>
       </c>
       <c r="B134" t="n">
-        <v>72.37999725341797</v>
+        <v>78.91999816894531</v>
       </c>
       <c r="C134" t="n">
-        <v>72.55000305175781</v>
+        <v>79.08999633789062</v>
       </c>
       <c r="D134" t="n">
-        <v>71.65000152587891</v>
+        <v>75.63999938964844</v>
       </c>
       <c r="E134" t="n">
-        <v>72.33000183105469</v>
+        <v>75.83999633789062</v>
       </c>
       <c r="F134" t="n">
-        <v>28418900</v>
+        <v>44225300</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="B135" t="n">
-        <v>73.12000274658203</v>
+        <v>78.84999847412109</v>
       </c>
       <c r="C135" t="n">
-        <v>73.5</v>
+        <v>79.63999938964844</v>
       </c>
       <c r="D135" t="n">
-        <v>72.30000305175781</v>
+        <v>78.51000213623047</v>
       </c>
       <c r="E135" t="n">
-        <v>72.40000152587891</v>
+        <v>78.90000152587891</v>
       </c>
       <c r="F135" t="n">
-        <v>24958100</v>
+        <v>35503900</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="B136" t="n">
-        <v>75.87000274658203</v>
+        <v>78.87999725341797</v>
       </c>
       <c r="C136" t="n">
-        <v>75.98999786376953</v>
+        <v>78.87999725341797</v>
       </c>
       <c r="D136" t="n">
-        <v>72.87999725341797</v>
+        <v>77.56999969482422</v>
       </c>
       <c r="E136" t="n">
-        <v>73.44999694824219</v>
+        <v>78.38999938964844</v>
       </c>
       <c r="F136" t="n">
-        <v>39536600</v>
+        <v>45910100</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="B137" t="n">
-        <v>76.31999969482422</v>
+        <v>78.56999969482422</v>
       </c>
       <c r="C137" t="n">
-        <v>77.33999633789062</v>
+        <v>78.65000152587891</v>
       </c>
       <c r="D137" t="n">
-        <v>75.62000274658203</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="E137" t="n">
-        <v>76.09999847412109</v>
+        <v>78.51999664306641</v>
       </c>
       <c r="F137" t="n">
-        <v>41501600</v>
+        <v>10678500</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>75.58000183105469</v>
+        <v>80.08000183105469</v>
       </c>
       <c r="C138" t="n">
-        <v>75.80000305175781</v>
+        <v>80.20999908447266</v>
       </c>
       <c r="D138" t="n">
-        <v>74.19000244140625</v>
+        <v>77.41000366210938</v>
       </c>
       <c r="E138" t="n">
-        <v>75.80000305175781</v>
+        <v>77.83000183105469</v>
       </c>
       <c r="F138" t="n">
-        <v>31894900</v>
+        <v>31198500</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>74.72000122070312</v>
+        <v>82.5</v>
       </c>
       <c r="C139" t="n">
-        <v>75.70999908447266</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="D139" t="n">
-        <v>74.19999694824219</v>
+        <v>80.5</v>
       </c>
       <c r="E139" t="n">
-        <v>74.90000152587891</v>
+        <v>80.98999786376953</v>
       </c>
       <c r="F139" t="n">
-        <v>24801200</v>
+        <v>83134600</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>74.73999786376953</v>
+        <v>82.98000335693359</v>
       </c>
       <c r="C140" t="n">
-        <v>75.47000122070312</v>
+        <v>84.40000152587891</v>
       </c>
       <c r="D140" t="n">
-        <v>74.51000213623047</v>
+        <v>82.08000183105469</v>
       </c>
       <c r="E140" t="n">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="F140" t="n">
-        <v>13129800</v>
+        <v>62515300</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>75.34999847412109</v>
+        <v>85.01999664306641</v>
       </c>
       <c r="C141" t="n">
-        <v>76.05000305175781</v>
+        <v>85.73999786376953</v>
       </c>
       <c r="D141" t="n">
-        <v>74.27999877929688</v>
+        <v>83.69000244140625</v>
       </c>
       <c r="E141" t="n">
-        <v>74.47000122070312</v>
+        <v>83.75</v>
       </c>
       <c r="F141" t="n">
-        <v>24539200</v>
+        <v>25432600</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46036</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>78.91999816894531</v>
+        <v>83.06999969482422</v>
       </c>
       <c r="C142" t="n">
-        <v>79.08999633789062</v>
+        <v>86.13999938964844</v>
       </c>
       <c r="D142" t="n">
-        <v>75.63999938964844</v>
+        <v>82.18000030517578</v>
       </c>
       <c r="E142" t="n">
-        <v>75.83999633789062</v>
+        <v>85.55999755859375</v>
       </c>
       <c r="F142" t="n">
-        <v>44225300</v>
+        <v>35741300</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>78.84999847412109</v>
+        <v>84.90000152587891</v>
       </c>
       <c r="C143" t="n">
-        <v>79.63999938964844</v>
+        <v>86.12999725341797</v>
       </c>
       <c r="D143" t="n">
-        <v>78.51000213623047</v>
+        <v>83.34999847412109</v>
       </c>
       <c r="E143" t="n">
-        <v>78.90000152587891</v>
+        <v>83.58999633789062</v>
       </c>
       <c r="F143" t="n">
-        <v>35503900</v>
+        <v>30922500</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>78.87999725341797</v>
+        <v>86.97000122070312</v>
       </c>
       <c r="C144" t="n">
-        <v>78.87999725341797</v>
+        <v>87.48999786376953</v>
       </c>
       <c r="D144" t="n">
-        <v>77.56999969482422</v>
+        <v>85</v>
       </c>
       <c r="E144" t="n">
-        <v>78.38999938964844</v>
+        <v>85.29000091552734</v>
       </c>
       <c r="F144" t="n">
-        <v>45910100</v>
+        <v>28473800</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>78.56999969482422</v>
+        <v>87.41000366210938</v>
       </c>
       <c r="C145" t="n">
-        <v>78.65000152587891</v>
+        <v>89.5</v>
       </c>
       <c r="D145" t="n">
-        <v>77.87000274658203</v>
+        <v>86.80999755859375</v>
       </c>
       <c r="E145" t="n">
-        <v>78.51999664306641</v>
+        <v>88</v>
       </c>
       <c r="F145" t="n">
-        <v>10678500</v>
+        <v>42013200</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>80.08000183105469</v>
+        <v>84.31999969482422</v>
       </c>
       <c r="C146" t="n">
-        <v>80.20999908447266</v>
+        <v>87.90000152587891</v>
       </c>
       <c r="D146" t="n">
-        <v>77.41000366210938</v>
+        <v>84</v>
       </c>
       <c r="E146" t="n">
-        <v>77.83000183105469</v>
+        <v>85.66999816894531</v>
       </c>
       <c r="F146" t="n">
-        <v>31198500</v>
+        <v>41681400</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>82.5</v>
+        <v>84.81999969482422</v>
       </c>
       <c r="C147" t="n">
-        <v>82.80000305175781</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="D147" t="n">
-        <v>80.5</v>
+        <v>84.04000091552734</v>
       </c>
       <c r="E147" t="n">
-        <v>80.98999786376953</v>
+        <v>84.41999816894531</v>
       </c>
       <c r="F147" t="n">
-        <v>83134600</v>
+        <v>22289400</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46044</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>82.98000335693359</v>
+        <v>88.98999786376953</v>
       </c>
       <c r="C148" t="n">
-        <v>84.40000152587891</v>
+        <v>89</v>
       </c>
       <c r="D148" t="n">
-        <v>82.08000183105469</v>
+        <v>86.41999816894531</v>
       </c>
       <c r="E148" t="n">
-        <v>82.5</v>
+        <v>86.41999816894531</v>
       </c>
       <c r="F148" t="n">
-        <v>62515300</v>
+        <v>37709700</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46045</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>85.01999664306641</v>
+        <v>89.43000030517578</v>
       </c>
       <c r="C149" t="n">
-        <v>85.73999786376953</v>
+        <v>89.58999633789062</v>
       </c>
       <c r="D149" t="n">
-        <v>83.69000244140625</v>
+        <v>87.55000305175781</v>
       </c>
       <c r="E149" t="n">
-        <v>83.75</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="F149" t="n">
-        <v>25432600</v>
+        <v>51744400</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46048</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>83.06999969482422</v>
+        <v>86.44999694824219</v>
       </c>
       <c r="C150" t="n">
-        <v>86.13999938964844</v>
+        <v>88.93000030517578</v>
       </c>
       <c r="D150" t="n">
-        <v>82.18000030517578</v>
+        <v>86.23999786376953</v>
       </c>
       <c r="E150" t="n">
-        <v>85.55999755859375</v>
+        <v>87.98999786376953</v>
       </c>
       <c r="F150" t="n">
-        <v>35741300</v>
+        <v>57049000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>84.90000152587891</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="C151" t="n">
-        <v>86.12999725341797</v>
+        <v>87.55999755859375</v>
       </c>
       <c r="D151" t="n">
-        <v>83.34999847412109</v>
+        <v>85.19999694824219</v>
       </c>
       <c r="E151" t="n">
-        <v>83.58999633789062</v>
+        <v>86.41000366210938</v>
       </c>
       <c r="F151" t="n">
-        <v>30922500</v>
+        <v>28889600</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>86.97000122070312</v>
+        <v>87.30999755859375</v>
       </c>
       <c r="C152" t="n">
-        <v>87.48999786376953</v>
+        <v>87.68000030517578</v>
       </c>
       <c r="D152" t="n">
-        <v>85</v>
+        <v>84.62999725341797</v>
       </c>
       <c r="E152" t="n">
-        <v>85.29000091552734</v>
+        <v>86.65000152587891</v>
       </c>
       <c r="F152" t="n">
-        <v>28473800</v>
+        <v>26531100</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46051</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>87.41000366210938</v>
+        <v>87.05000305175781</v>
       </c>
       <c r="C153" t="n">
-        <v>89.5</v>
+        <v>87.73999786376953</v>
       </c>
       <c r="D153" t="n">
-        <v>86.80999755859375</v>
+        <v>86.25</v>
       </c>
       <c r="E153" t="n">
-        <v>88</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="F153" t="n">
-        <v>42013200</v>
+        <v>14177200</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>84.31999969482422</v>
+        <v>90.08999633789062</v>
       </c>
       <c r="C154" t="n">
-        <v>87.90000152587891</v>
+        <v>90.31999969482422</v>
       </c>
       <c r="D154" t="n">
-        <v>84</v>
+        <v>88.48000335693359</v>
       </c>
       <c r="E154" t="n">
-        <v>85.66999816894531</v>
+        <v>88.65000152587891</v>
       </c>
       <c r="F154" t="n">
-        <v>41681400</v>
+        <v>28395300</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>84.81999969482422</v>
+        <v>89.23000335693359</v>
       </c>
       <c r="C155" t="n">
-        <v>85.84999847412109</v>
+        <v>91.62000274658203</v>
       </c>
       <c r="D155" t="n">
-        <v>84.04000091552734</v>
+        <v>89.08000183105469</v>
       </c>
       <c r="E155" t="n">
-        <v>84.41999816894531</v>
+        <v>89.84999847412109</v>
       </c>
       <c r="F155" t="n">
-        <v>22289400</v>
+        <v>51472200</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>88.98999786376953</v>
+        <v>87.02999877929688</v>
       </c>
       <c r="C156" t="n">
-        <v>89</v>
+        <v>88.13999938964844</v>
       </c>
       <c r="D156" t="n">
-        <v>86.41999816894531</v>
+        <v>86.01999664306641</v>
       </c>
       <c r="E156" t="n">
-        <v>86.41999816894531</v>
+        <v>87.56999969482422</v>
       </c>
       <c r="F156" t="n">
-        <v>37709700</v>
+        <v>28644800</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="B157" t="n">
-        <v>89.43000030517578</v>
+        <v>83.91999816894531</v>
       </c>
       <c r="C157" t="n">
-        <v>89.58999633789062</v>
+        <v>85.15000152587891</v>
       </c>
       <c r="D157" t="n">
-        <v>87.55000305175781</v>
+        <v>83.55999755859375</v>
       </c>
       <c r="E157" t="n">
-        <v>88.51000213623047</v>
+        <v>85.09999847412109</v>
       </c>
       <c r="F157" t="n">
-        <v>51744400</v>
+        <v>20898700</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46058</v>
+        <v>46072</v>
       </c>
       <c r="B158" t="n">
-        <v>86.44999694824219</v>
+        <v>83.45999908447266</v>
       </c>
       <c r="C158" t="n">
-        <v>88.93000030517578</v>
+        <v>84.34999847412109</v>
       </c>
       <c r="D158" t="n">
-        <v>86.23999786376953</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="E158" t="n">
-        <v>87.98999786376953</v>
+        <v>83.02999877929688</v>
       </c>
       <c r="F158" t="n">
-        <v>57049000</v>
+        <v>28410900</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B159" t="n">
-        <v>85.62999725341797</v>
+        <v>86.80999755859375</v>
       </c>
       <c r="C159" t="n">
-        <v>87.55999755859375</v>
+        <v>86.80999755859375</v>
       </c>
       <c r="D159" t="n">
-        <v>85.19999694824219</v>
+        <v>83.41999816894531</v>
       </c>
       <c r="E159" t="n">
-        <v>86.41000366210938</v>
+        <v>83.80000305175781</v>
       </c>
       <c r="F159" t="n">
-        <v>28889600</v>
+        <v>40577200</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="B160" t="n">
-        <v>87.30999755859375</v>
+        <v>87.38999938964844</v>
       </c>
       <c r="C160" t="n">
-        <v>87.68000030517578</v>
+        <v>88.31999969482422</v>
       </c>
       <c r="D160" t="n">
-        <v>84.62999725341797</v>
+        <v>86.41999816894531</v>
       </c>
       <c r="E160" t="n">
-        <v>86.65000152587891</v>
+        <v>86.80999755859375</v>
       </c>
       <c r="F160" t="n">
-        <v>26531100</v>
+        <v>21193900</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="B161" t="n">
-        <v>87.05000305175781</v>
+        <v>87.73000335693359</v>
       </c>
       <c r="C161" t="n">
-        <v>87.73999786376953</v>
+        <v>88.70999908447266</v>
       </c>
       <c r="D161" t="n">
-        <v>86.25</v>
+        <v>87.40000152587891</v>
       </c>
       <c r="E161" t="n">
-        <v>86.72000122070312</v>
+        <v>87.40000152587891</v>
       </c>
       <c r="F161" t="n">
-        <v>14177200</v>
+        <v>19760700</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="B162" t="n">
-        <v>90.08999633789062</v>
+        <v>89.97000122070312</v>
       </c>
       <c r="C162" t="n">
-        <v>90.31999969482422</v>
+        <v>90.33000183105469</v>
       </c>
       <c r="D162" t="n">
-        <v>88.48000335693359</v>
+        <v>88.51000213623047</v>
       </c>
       <c r="E162" t="n">
-        <v>88.65000152587891</v>
+        <v>89.02999877929688</v>
       </c>
       <c r="F162" t="n">
-        <v>28395300</v>
+        <v>28707500</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46065</v>
+        <v>46079</v>
       </c>
       <c r="B163" t="n">
-        <v>89.23000335693359</v>
+        <v>89.20999908447266</v>
       </c>
       <c r="C163" t="n">
-        <v>91.62000274658203</v>
+        <v>89.37999725341797</v>
       </c>
       <c r="D163" t="n">
-        <v>89.08000183105469</v>
+        <v>87.04000091552734</v>
       </c>
       <c r="E163" t="n">
-        <v>89.84999847412109</v>
+        <v>88.94000244140625</v>
       </c>
       <c r="F163" t="n">
-        <v>51472200</v>
+        <v>24503100</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="B164" t="n">
-        <v>87.02999877929688</v>
+        <v>88.47000122070312</v>
       </c>
       <c r="C164" t="n">
-        <v>88.13999938964844</v>
+        <v>89.5</v>
       </c>
       <c r="D164" t="n">
-        <v>86.01999664306641</v>
+        <v>88.26000213623047</v>
       </c>
       <c r="E164" t="n">
-        <v>87.56999969482422</v>
+        <v>89.13999938964844</v>
       </c>
       <c r="F164" t="n">
-        <v>28644800</v>
+        <v>17328300</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46071</v>
+        <v>46083</v>
       </c>
       <c r="B165" t="n">
-        <v>83.91999816894531</v>
+        <v>88.16000366210938</v>
       </c>
       <c r="C165" t="n">
-        <v>85.15000152587891</v>
+        <v>89.16000366210938</v>
       </c>
       <c r="D165" t="n">
-        <v>83.55999755859375</v>
+        <v>87.29000091552734</v>
       </c>
       <c r="E165" t="n">
-        <v>85.09999847412109</v>
+        <v>87.91999816894531</v>
       </c>
       <c r="F165" t="n">
-        <v>20898700</v>
+        <v>13952600</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46072</v>
+        <v>46084</v>
       </c>
       <c r="B166" t="n">
-        <v>83.45999908447266</v>
+        <v>84.48000335693359</v>
       </c>
       <c r="C166" t="n">
-        <v>84.34999847412109</v>
+        <v>85.30999755859375</v>
       </c>
       <c r="D166" t="n">
-        <v>82.33000183105469</v>
+        <v>82.55000305175781</v>
       </c>
       <c r="E166" t="n">
-        <v>83.02999877929688</v>
+        <v>85.25</v>
       </c>
       <c r="F166" t="n">
-        <v>28410900</v>
+        <v>36088800</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46073</v>
+        <v>46085</v>
       </c>
       <c r="B167" t="n">
-        <v>86.80999755859375</v>
+        <v>84.08999633789062</v>
       </c>
       <c r="C167" t="n">
-        <v>86.80999755859375</v>
+        <v>85.62999725341797</v>
       </c>
       <c r="D167" t="n">
-        <v>83.41999816894531</v>
+        <v>83.58000183105469</v>
       </c>
       <c r="E167" t="n">
-        <v>83.80000305175781</v>
+        <v>85.38999938964844</v>
       </c>
       <c r="F167" t="n">
-        <v>40577200</v>
+        <v>17605800</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="B168" t="n">
-        <v>87.38999938964844</v>
+        <v>81.29000091552734</v>
       </c>
       <c r="C168" t="n">
-        <v>88.31999969482422</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="D168" t="n">
-        <v>86.41999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="E168" t="n">
-        <v>86.80999755859375</v>
+        <v>84.12999725341797</v>
       </c>
       <c r="F168" t="n">
-        <v>21193900</v>
+        <v>37872100</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="B169" t="n">
-        <v>87.73000335693359</v>
+        <v>78.86000061035156</v>
       </c>
       <c r="C169" t="n">
-        <v>88.70999908447266</v>
+        <v>81.19999694824219</v>
       </c>
       <c r="D169" t="n">
-        <v>87.40000152587891</v>
+        <v>78.40000152587891</v>
       </c>
       <c r="E169" t="n">
-        <v>87.40000152587891</v>
+        <v>80.90000152587891</v>
       </c>
       <c r="F169" t="n">
-        <v>19760700</v>
+        <v>29504600</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="B170" t="n">
-        <v>89.97000122070312</v>
+        <v>79.26000213623047</v>
       </c>
       <c r="C170" t="n">
-        <v>90.33000183105469</v>
+        <v>80.09999847412109</v>
       </c>
       <c r="D170" t="n">
-        <v>88.51000213623047</v>
+        <v>76.55000305175781</v>
       </c>
       <c r="E170" t="n">
-        <v>89.02999877929688</v>
+        <v>77.72000122070312</v>
       </c>
       <c r="F170" t="n">
-        <v>28707500</v>
+        <v>30576600</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="B171" t="n">
-        <v>89.20999908447266</v>
+        <v>80.55999755859375</v>
       </c>
       <c r="C171" t="n">
-        <v>89.37999725341797</v>
+        <v>80.98999786376953</v>
       </c>
       <c r="D171" t="n">
-        <v>87.04000091552734</v>
+        <v>79.66999816894531</v>
       </c>
       <c r="E171" t="n">
-        <v>88.94000244140625</v>
+        <v>80.16000366210938</v>
       </c>
       <c r="F171" t="n">
-        <v>24503100</v>
+        <v>17172800</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46080</v>
+        <v>46092</v>
       </c>
       <c r="B172" t="n">
-        <v>88.47000122070312</v>
+        <v>79.84999847412109</v>
       </c>
       <c r="C172" t="n">
-        <v>89.5</v>
+        <v>80.94000244140625</v>
       </c>
       <c r="D172" t="n">
-        <v>88.26000213623047</v>
+        <v>78.80000305175781</v>
       </c>
       <c r="E172" t="n">
-        <v>89.13999938964844</v>
+        <v>79.79000091552734</v>
       </c>
       <c r="F172" t="n">
-        <v>17328300</v>
+        <v>20865000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="B173" t="n">
-        <v>88.16000366210938</v>
+        <v>79.23999786376953</v>
       </c>
       <c r="C173" t="n">
-        <v>89.16000366210938</v>
+        <v>79.76999664306641</v>
       </c>
       <c r="D173" t="n">
-        <v>87.29000091552734</v>
+        <v>77.66000366210938</v>
       </c>
       <c r="E173" t="n">
-        <v>87.91999816894531</v>
+        <v>79.76999664306641</v>
       </c>
       <c r="F173" t="n">
-        <v>13952600</v>
+        <v>29136500</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="B174" t="n">
-        <v>84.48000335693359</v>
+        <v>78.30000305175781</v>
       </c>
       <c r="C174" t="n">
-        <v>85.30999755859375</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="D174" t="n">
-        <v>82.55000305175781</v>
+        <v>78.01999664306641</v>
       </c>
       <c r="E174" t="n">
-        <v>85.25</v>
+        <v>79.30000305175781</v>
       </c>
       <c r="F174" t="n">
-        <v>36088800</v>
+        <v>14416400</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B175" t="n">
-        <v>84.08999633789062</v>
+        <v>78.83999633789062</v>
       </c>
       <c r="C175" t="n">
-        <v>85.62999725341797</v>
+        <v>80.19999694824219</v>
       </c>
       <c r="D175" t="n">
-        <v>83.58000183105469</v>
+        <v>78.80999755859375</v>
       </c>
       <c r="E175" t="n">
-        <v>85.38999938964844</v>
+        <v>79.38999938964844</v>
       </c>
       <c r="F175" t="n">
-        <v>17605800</v>
+        <v>13591400</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="B176" t="n">
-        <v>81.29000091552734</v>
+        <v>78.95999908447266</v>
       </c>
       <c r="C176" t="n">
-        <v>84.30000305175781</v>
+        <v>79.70999908447266</v>
       </c>
       <c r="D176" t="n">
-        <v>80.55000305175781</v>
+        <v>78.62999725341797</v>
       </c>
       <c r="E176" t="n">
-        <v>84.12999725341797</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="F176" t="n">
-        <v>37872100</v>
+        <v>14222300</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="B177" t="n">
-        <v>78.86000061035156</v>
+        <v>77.12999725341797</v>
       </c>
       <c r="C177" t="n">
-        <v>81.19999694824219</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="D177" t="n">
-        <v>78.40000152587891</v>
+        <v>77.05000305175781</v>
       </c>
       <c r="E177" t="n">
-        <v>80.90000152587891</v>
+        <v>78.65000152587891</v>
       </c>
       <c r="F177" t="n">
-        <v>29504600</v>
+        <v>19412200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="B178" t="n">
-        <v>79.26000213623047</v>
+        <v>76.62999725341797</v>
       </c>
       <c r="C178" t="n">
-        <v>80.09999847412109</v>
+        <v>76.70999908447266</v>
       </c>
       <c r="D178" t="n">
-        <v>76.55000305175781</v>
+        <v>74.05999755859375</v>
       </c>
       <c r="E178" t="n">
-        <v>77.72000122070312</v>
+        <v>74.16999816894531</v>
       </c>
       <c r="F178" t="n">
-        <v>30576600</v>
+        <v>27262900</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="B179" t="n">
-        <v>80.55999755859375</v>
+        <v>75.55000305175781</v>
       </c>
       <c r="C179" t="n">
-        <v>80.98999786376953</v>
+        <v>76.69999694824219</v>
       </c>
       <c r="D179" t="n">
-        <v>79.66999816894531</v>
+        <v>74.70999908447266</v>
       </c>
       <c r="E179" t="n">
-        <v>80.16000366210938</v>
+        <v>76.20999908447266</v>
       </c>
       <c r="F179" t="n">
-        <v>17172800</v>
+        <v>44208900</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46092</v>
+        <v>46104</v>
       </c>
       <c r="B180" t="n">
-        <v>79.84999847412109</v>
+        <v>77.48999786376953</v>
       </c>
       <c r="C180" t="n">
-        <v>80.94000244140625</v>
+        <v>78.41999816894531</v>
       </c>
       <c r="D180" t="n">
-        <v>78.80000305175781</v>
+        <v>75.97000122070312</v>
       </c>
       <c r="E180" t="n">
-        <v>79.79000091552734</v>
+        <v>76.55999755859375</v>
       </c>
       <c r="F180" t="n">
-        <v>20865000</v>
+        <v>23384500</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="B181" t="n">
-        <v>79.23999786376953</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="C181" t="n">
-        <v>79.76999664306641</v>
+        <v>78.41000366210938</v>
       </c>
       <c r="D181" t="n">
-        <v>77.66000366210938</v>
+        <v>76.55999755859375</v>
       </c>
       <c r="E181" t="n">
-        <v>79.76999664306641</v>
+        <v>76.98000335693359</v>
       </c>
       <c r="F181" t="n">
-        <v>29136500</v>
+        <v>15700300</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="B182" t="n">
-        <v>78.30000305175781</v>
+        <v>79.55000305175781</v>
       </c>
       <c r="C182" t="n">
-        <v>80.48999786376953</v>
+        <v>80.25</v>
       </c>
       <c r="D182" t="n">
-        <v>78.01999664306641</v>
+        <v>79</v>
       </c>
       <c r="E182" t="n">
-        <v>79.30000305175781</v>
+        <v>79.19999694824219</v>
       </c>
       <c r="F182" t="n">
-        <v>14416400</v>
+        <v>18658300</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="B183" t="n">
-        <v>78.83999633789062</v>
+        <v>78.91000366210938</v>
       </c>
       <c r="C183" t="n">
-        <v>80.19999694824219</v>
+        <v>79.58999633789062</v>
       </c>
       <c r="D183" t="n">
-        <v>78.80999755859375</v>
+        <v>78.01000213623047</v>
       </c>
       <c r="E183" t="n">
-        <v>79.38999938964844</v>
+        <v>78.12999725341797</v>
       </c>
       <c r="F183" t="n">
-        <v>13591400</v>
+        <v>13518900</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="B184" t="n">
-        <v>78.95999908447266</v>
+        <v>79</v>
       </c>
       <c r="C184" t="n">
-        <v>79.70999908447266</v>
+        <v>79.91999816894531</v>
       </c>
       <c r="D184" t="n">
-        <v>78.62999725341797</v>
+        <v>78.16999816894531</v>
       </c>
       <c r="E184" t="n">
-        <v>79.09999847412109</v>
+        <v>78.47000122070312</v>
       </c>
       <c r="F184" t="n">
-        <v>14222300</v>
+        <v>11101700</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46099</v>
+        <v>46111</v>
       </c>
       <c r="B185" t="n">
-        <v>77.12999725341797</v>
+        <v>79.5</v>
       </c>
       <c r="C185" t="n">
-        <v>78.66999816894531</v>
+        <v>81.05999755859375</v>
       </c>
       <c r="D185" t="n">
-        <v>77.05000305175781</v>
+        <v>79.29000091552734</v>
       </c>
       <c r="E185" t="n">
-        <v>78.65000152587891</v>
+        <v>80.25</v>
       </c>
       <c r="F185" t="n">
-        <v>19412200</v>
+        <v>18776700</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="B186" t="n">
-        <v>76.62999725341797</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="C186" t="n">
-        <v>76.70999908447266</v>
+        <v>82.73999786376953</v>
       </c>
       <c r="D186" t="n">
-        <v>74.05999755859375</v>
+        <v>80.58999633789062</v>
       </c>
       <c r="E186" t="n">
-        <v>74.16999816894531</v>
+        <v>80.73999786376953</v>
       </c>
       <c r="F186" t="n">
-        <v>27262900</v>
+        <v>24956400</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="B187" t="n">
-        <v>75.55000305175781</v>
+        <v>83</v>
       </c>
       <c r="C187" t="n">
-        <v>76.69999694824219</v>
+        <v>84.04000091552734</v>
       </c>
       <c r="D187" t="n">
-        <v>74.70999908447266</v>
+        <v>82.58000183105469</v>
       </c>
       <c r="E187" t="n">
-        <v>76.20999908447266</v>
+        <v>83.30999755859375</v>
       </c>
       <c r="F187" t="n">
-        <v>44208900</v>
+        <v>28514000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46104</v>
+        <v>46114</v>
       </c>
       <c r="B188" t="n">
-        <v>77.48999786376953</v>
+        <v>83.55000305175781</v>
       </c>
       <c r="C188" t="n">
-        <v>78.41999816894531</v>
+        <v>83.76999664306641</v>
       </c>
       <c r="D188" t="n">
-        <v>75.97000122070312</v>
+        <v>81.36000061035156</v>
       </c>
       <c r="E188" t="n">
-        <v>76.55999755859375</v>
+        <v>81.51000213623047</v>
       </c>
       <c r="F188" t="n">
-        <v>23384500</v>
+        <v>14019800</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46105</v>
+        <v>46118</v>
       </c>
       <c r="B189" t="n">
-        <v>78.09999847412109</v>
+        <v>83.08999633789062</v>
       </c>
       <c r="C189" t="n">
-        <v>78.41000366210938</v>
+        <v>84.22000122070312</v>
       </c>
       <c r="D189" t="n">
-        <v>76.55999755859375</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="E189" t="n">
-        <v>76.98000335693359</v>
+        <v>84.04000091552734</v>
       </c>
       <c r="F189" t="n">
-        <v>15700300</v>
+        <v>8680700</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="B190" t="n">
-        <v>79.55000305175781</v>
+        <v>83.69000244140625</v>
       </c>
       <c r="C190" t="n">
-        <v>80.25</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="D190" t="n">
-        <v>79</v>
+        <v>82.59999847412109</v>
       </c>
       <c r="E190" t="n">
-        <v>79.19999694824219</v>
+        <v>83.05000305175781</v>
       </c>
       <c r="F190" t="n">
-        <v>18658300</v>
+        <v>15312500</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="B191" t="n">
-        <v>78.91000366210938</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="C191" t="n">
-        <v>79.58999633789062</v>
+        <v>86.72000122070312</v>
       </c>
       <c r="D191" t="n">
-        <v>78.01000213623047</v>
+        <v>84.73000335693359</v>
       </c>
       <c r="E191" t="n">
-        <v>78.12999725341797</v>
+        <v>86.5</v>
       </c>
       <c r="F191" t="n">
-        <v>13518900</v>
+        <v>24942400</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="B192" t="n">
-        <v>79</v>
+        <v>84.69000244140625</v>
       </c>
       <c r="C192" t="n">
-        <v>79.91999816894531</v>
+        <v>85.54000091552734</v>
       </c>
       <c r="D192" t="n">
-        <v>78.16999816894531</v>
+        <v>84.26000213623047</v>
       </c>
       <c r="E192" t="n">
-        <v>78.47000122070312</v>
+        <v>85.36000061035156</v>
       </c>
       <c r="F192" t="n">
-        <v>11101700</v>
+        <v>17973100</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="B193" t="n">
-        <v>79.5</v>
+        <v>85.58999633789062</v>
       </c>
       <c r="C193" t="n">
-        <v>81.05999755859375</v>
+        <v>86.38999938964844</v>
       </c>
       <c r="D193" t="n">
-        <v>79.29000091552734</v>
+        <v>84.58000183105469</v>
       </c>
       <c r="E193" t="n">
-        <v>80.25</v>
+        <v>85</v>
       </c>
       <c r="F193" t="n">
-        <v>18776700</v>
+        <v>24002400</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46112</v>
+        <v>46125</v>
       </c>
       <c r="B194" t="n">
-        <v>82.48000335693359</v>
+        <v>87.36000061035156</v>
       </c>
       <c r="C194" t="n">
-        <v>82.73999786376953</v>
+        <v>87.36000061035156</v>
       </c>
       <c r="D194" t="n">
-        <v>80.58999633789062</v>
+        <v>84.91999816894531</v>
       </c>
       <c r="E194" t="n">
-        <v>80.73999786376953</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="F194" t="n">
-        <v>24956400</v>
+        <v>24661900</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="B195" t="n">
-        <v>83</v>
+        <v>88.30000305175781</v>
       </c>
       <c r="C195" t="n">
-        <v>84.04000091552734</v>
+        <v>88.54000091552734</v>
       </c>
       <c r="D195" t="n">
-        <v>82.58000183105469</v>
+        <v>87.18000030517578</v>
       </c>
       <c r="E195" t="n">
-        <v>83.30999755859375</v>
+        <v>87.5</v>
       </c>
       <c r="F195" t="n">
-        <v>28514000</v>
+        <v>18528400</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="B196" t="n">
-        <v>83.55000305175781</v>
+        <v>88.44000244140625</v>
       </c>
       <c r="C196" t="n">
-        <v>83.76999664306641</v>
+        <v>89.08000183105469</v>
       </c>
       <c r="D196" t="n">
-        <v>81.36000061035156</v>
+        <v>87.88999938964844</v>
       </c>
       <c r="E196" t="n">
-        <v>81.51000213623047</v>
+        <v>88.15000152587891</v>
       </c>
       <c r="F196" t="n">
-        <v>14019800</v>
+        <v>24527300</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="B197" t="n">
-        <v>83.08999633789062</v>
+        <v>87.44000244140625</v>
       </c>
       <c r="C197" t="n">
-        <v>84.22000122070312</v>
+        <v>89.38999938964844</v>
       </c>
       <c r="D197" t="n">
-        <v>82.80000305175781</v>
+        <v>87.09999847412109</v>
       </c>
       <c r="E197" t="n">
-        <v>84.04000091552734</v>
+        <v>88.88999938964844</v>
       </c>
       <c r="F197" t="n">
-        <v>8680700</v>
+        <v>13618900</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="B198" t="n">
-        <v>83.69000244140625</v>
+        <v>89.75</v>
       </c>
       <c r="C198" t="n">
-        <v>83.69999694824219</v>
+        <v>89.75</v>
       </c>
       <c r="D198" t="n">
-        <v>82.59999847412109</v>
+        <v>87.80000305175781</v>
       </c>
       <c r="E198" t="n">
-        <v>83.05000305175781</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="F198" t="n">
-        <v>15312500</v>
+        <v>30119000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="B199" t="n">
-        <v>85.58999633789062</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="C199" t="n">
-        <v>86.72000122070312</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="D199" t="n">
-        <v>84.73000335693359</v>
+        <v>88.02999877929688</v>
       </c>
       <c r="E199" t="n">
-        <v>86.5</v>
+        <v>88.80000305175781</v>
       </c>
       <c r="F199" t="n">
-        <v>24942400</v>
+        <v>16067700</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="B200" t="n">
-        <v>84.69000244140625</v>
+        <v>87.22000122070312</v>
       </c>
       <c r="C200" t="n">
-        <v>85.54000091552734</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="D200" t="n">
-        <v>84.26000213623047</v>
+        <v>87.22000122070312</v>
       </c>
       <c r="E200" t="n">
-        <v>85.36000061035156</v>
+        <v>87.94999694824219</v>
       </c>
       <c r="F200" t="n">
-        <v>17973100</v>
+        <v>13222100</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="B201" t="n">
-        <v>85.58999633789062</v>
+        <v>85.97000122070312</v>
       </c>
       <c r="C201" t="n">
-        <v>86.38999938964844</v>
+        <v>87.16999816894531</v>
       </c>
       <c r="D201" t="n">
-        <v>84.58000183105469</v>
+        <v>85.70999908447266</v>
       </c>
       <c r="E201" t="n">
-        <v>85</v>
+        <v>86.63999938964844</v>
       </c>
       <c r="F201" t="n">
-        <v>24002400</v>
+        <v>12637500</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="B202" t="n">
-        <v>87.36000061035156</v>
+        <v>85.87000274658203</v>
       </c>
       <c r="C202" t="n">
-        <v>87.36000061035156</v>
+        <v>86.98999786376953</v>
       </c>
       <c r="D202" t="n">
-        <v>84.91999816894531</v>
+        <v>85.75</v>
       </c>
       <c r="E202" t="n">
-        <v>85.11000061035156</v>
+        <v>85.97000122070312</v>
       </c>
       <c r="F202" t="n">
-        <v>24661900</v>
+        <v>11436400</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="B203" t="n">
-        <v>88.30000305175781</v>
+        <v>85.5</v>
       </c>
       <c r="C203" t="n">
-        <v>88.54000091552734</v>
+        <v>86.30000305175781</v>
       </c>
       <c r="D203" t="n">
-        <v>87.18000030517578</v>
+        <v>84.88999938964844</v>
       </c>
       <c r="E203" t="n">
-        <v>87.5</v>
+        <v>86.15000152587891</v>
       </c>
       <c r="F203" t="n">
-        <v>18528400</v>
+        <v>8656600</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="B204" t="n">
-        <v>88.44000244140625</v>
+        <v>84.38999938964844</v>
       </c>
       <c r="C204" t="n">
-        <v>89.08000183105469</v>
+        <v>85.30000305175781</v>
       </c>
       <c r="D204" t="n">
-        <v>87.88999938964844</v>
+        <v>84.05000305175781</v>
       </c>
       <c r="E204" t="n">
-        <v>88.15000152587891</v>
+        <v>84.69999694824219</v>
       </c>
       <c r="F204" t="n">
-        <v>24527300</v>
+        <v>13687500</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="B205" t="n">
-        <v>87.44000244140625</v>
+        <v>79.44000244140625</v>
       </c>
       <c r="C205" t="n">
-        <v>89.38999938964844</v>
+        <v>82.91000366210938</v>
       </c>
       <c r="D205" t="n">
-        <v>87.09999847412109</v>
+        <v>79.25</v>
       </c>
       <c r="E205" t="n">
-        <v>88.88999938964844</v>
+        <v>82.80000305175781</v>
       </c>
       <c r="F205" t="n">
-        <v>13618900</v>
+        <v>43296200</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="B206" t="n">
-        <v>89.75</v>
+        <v>81.18000030517578</v>
       </c>
       <c r="C206" t="n">
-        <v>89.75</v>
+        <v>81.69999694824219</v>
       </c>
       <c r="D206" t="n">
-        <v>87.80000305175781</v>
+        <v>80.20999908447266</v>
       </c>
       <c r="E206" t="n">
-        <v>88.19999694824219</v>
+        <v>81.02999877929688</v>
       </c>
       <c r="F206" t="n">
-        <v>30119000</v>
+        <v>17593900</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B207" t="n">
-        <v>88.73000335693359</v>
+        <v>78.66000366210938</v>
       </c>
       <c r="C207" t="n">
-        <v>89.44000244140625</v>
+        <v>81.36000061035156</v>
       </c>
       <c r="D207" t="n">
-        <v>88.02999877929688</v>
+        <v>78.65000152587891</v>
       </c>
       <c r="E207" t="n">
-        <v>88.80000305175781</v>
+        <v>81.18000030517578</v>
       </c>
       <c r="F207" t="n">
-        <v>16067700</v>
+        <v>18555600</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="B208" t="n">
-        <v>87.22000122070312</v>
+        <v>78.38999938964844</v>
       </c>
       <c r="C208" t="n">
-        <v>88.73000335693359</v>
+        <v>79.41999816894531</v>
       </c>
       <c r="D208" t="n">
-        <v>87.22000122070312</v>
+        <v>77.97000122070312</v>
       </c>
       <c r="E208" t="n">
-        <v>87.94999694824219</v>
+        <v>79.41999816894531</v>
       </c>
       <c r="F208" t="n">
-        <v>13222100</v>
+        <v>16295600</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="B209" t="n">
-        <v>85.97000122070312</v>
+        <v>81.23000335693359</v>
       </c>
       <c r="C209" t="n">
-        <v>87.16999816894531</v>
+        <v>81.63999938964844</v>
       </c>
       <c r="D209" t="n">
-        <v>85.70999908447266</v>
+        <v>80.09999847412109</v>
       </c>
       <c r="E209" t="n">
-        <v>86.63999938964844</v>
+        <v>80.34999847412109</v>
       </c>
       <c r="F209" t="n">
-        <v>12637500</v>
+        <v>17424200</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="B210" t="n">
-        <v>85.87000274658203</v>
+        <v>80.06999969482422</v>
       </c>
       <c r="C210" t="n">
-        <v>86.98999786376953</v>
+        <v>81.66999816894531</v>
       </c>
       <c r="D210" t="n">
-        <v>85.75</v>
+        <v>79.59999847412109</v>
       </c>
       <c r="E210" t="n">
-        <v>85.97000122070312</v>
+        <v>81.29000091552734</v>
       </c>
       <c r="F210" t="n">
-        <v>11436400</v>
+        <v>18912100</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="B211" t="n">
-        <v>85.5</v>
+        <v>80.80000305175781</v>
       </c>
       <c r="C211" t="n">
-        <v>86.30000305175781</v>
+        <v>81.79000091552734</v>
       </c>
       <c r="D211" t="n">
-        <v>84.88999938964844</v>
+        <v>80.36000061035156</v>
       </c>
       <c r="E211" t="n">
-        <v>86.15000152587891</v>
+        <v>80.56999969482422</v>
       </c>
       <c r="F211" t="n">
-        <v>8656600</v>
+        <v>16782600</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="B212" t="n">
-        <v>84.38999938964844</v>
+        <v>83.44999694824219</v>
       </c>
       <c r="C212" t="n">
-        <v>85.30000305175781</v>
+        <v>83.93000030517578</v>
       </c>
       <c r="D212" t="n">
-        <v>84.05000305175781</v>
+        <v>81.19000244140625</v>
       </c>
       <c r="E212" t="n">
-        <v>84.69999694824219</v>
+        <v>81.38999938964844</v>
       </c>
       <c r="F212" t="n">
-        <v>13687500</v>
+        <v>24868900</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="B213" t="n">
-        <v>79.44000244140625</v>
+        <v>83.25</v>
       </c>
       <c r="C213" t="n">
-        <v>82.91000366210938</v>
+        <v>83.98999786376953</v>
       </c>
       <c r="D213" t="n">
-        <v>79.25</v>
+        <v>81.73999786376953</v>
       </c>
       <c r="E213" t="n">
-        <v>82.80000305175781</v>
+        <v>83.15000152587891</v>
       </c>
       <c r="F213" t="n">
-        <v>43296200</v>
+        <v>16503000</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="B214" t="n">
-        <v>81.18000030517578</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="C214" t="n">
-        <v>81.69999694824219</v>
+        <v>85.05000305175781</v>
       </c>
       <c r="D214" t="n">
-        <v>80.20999908447266</v>
+        <v>83.01000213623047</v>
       </c>
       <c r="E214" t="n">
-        <v>81.02999877929688</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="F214" t="n">
-        <v>17593900</v>
+        <v>31641800</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="B215" t="n">
-        <v>78.66000366210938</v>
+        <v>82.87000274658203</v>
       </c>
       <c r="C215" t="n">
-        <v>81.36000061035156</v>
+        <v>85.41000366210938</v>
       </c>
       <c r="D215" t="n">
-        <v>78.65000152587891</v>
+        <v>82.62999725341797</v>
       </c>
       <c r="E215" t="n">
-        <v>81.18000030517578</v>
+        <v>85</v>
       </c>
       <c r="F215" t="n">
-        <v>18555600</v>
+        <v>31954300</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="B216" t="n">
-        <v>78.38999938964844</v>
+        <v>83.5</v>
       </c>
       <c r="C216" t="n">
-        <v>79.41999816894531</v>
+        <v>83.5</v>
       </c>
       <c r="D216" t="n">
-        <v>77.97000122070312</v>
+        <v>80.23999786376953</v>
       </c>
       <c r="E216" t="n">
-        <v>79.41999816894531</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="F216" t="n">
-        <v>16295600</v>
+        <v>36318900</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="B217" t="n">
-        <v>81.23000335693359</v>
+        <v>81.83000183105469</v>
       </c>
       <c r="C217" t="n">
-        <v>81.63999938964844</v>
+        <v>83.59999847412109</v>
       </c>
       <c r="D217" t="n">
-        <v>80.09999847412109</v>
+        <v>81.05999755859375</v>
       </c>
       <c r="E217" t="n">
-        <v>80.34999847412109</v>
+        <v>83</v>
       </c>
       <c r="F217" t="n">
-        <v>17424200</v>
+        <v>22668800</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="B218" t="n">
-        <v>80.06999969482422</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="C218" t="n">
-        <v>81.66999816894531</v>
+        <v>81.27999877929688</v>
       </c>
       <c r="D218" t="n">
-        <v>79.59999847412109</v>
+        <v>80.16999816894531</v>
       </c>
       <c r="E218" t="n">
-        <v>81.29000091552734</v>
+        <v>80.80000305175781</v>
       </c>
       <c r="F218" t="n">
-        <v>18912100</v>
+        <v>20334400</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="B219" t="n">
-        <v>80.80000305175781</v>
+        <v>82</v>
       </c>
       <c r="C219" t="n">
-        <v>81.79000091552734</v>
+        <v>82.20999908447266</v>
       </c>
       <c r="D219" t="n">
-        <v>80.36000061035156</v>
+        <v>80.84999847412109</v>
       </c>
       <c r="E219" t="n">
-        <v>80.56999969482422</v>
+        <v>81.44999694824219</v>
       </c>
       <c r="F219" t="n">
-        <v>16782600</v>
+        <v>15669300</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B220" t="n">
-        <v>83.44999694824219</v>
+        <v>82.62999725341797</v>
       </c>
       <c r="C220" t="n">
-        <v>83.93000030517578</v>
+        <v>82.87999725341797</v>
       </c>
       <c r="D220" t="n">
-        <v>81.19000244140625</v>
+        <v>81.22000122070312</v>
       </c>
       <c r="E220" t="n">
-        <v>81.38999938964844</v>
+        <v>81.36000061035156</v>
       </c>
       <c r="F220" t="n">
-        <v>24868900</v>
+        <v>15156600</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B221" t="n">
-        <v>83.25</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="C221" t="n">
-        <v>83.98999786376953</v>
+        <v>83.13999938964844</v>
       </c>
       <c r="D221" t="n">
-        <v>81.73999786376953</v>
+        <v>81.84999847412109</v>
       </c>
       <c r="E221" t="n">
-        <v>83.15000152587891</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="F221" t="n">
-        <v>16503000</v>
+        <v>11443900</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B222" t="n">
-        <v>84.30000305175781</v>
+        <v>83.58999633789062</v>
       </c>
       <c r="C222" t="n">
-        <v>85.05000305175781</v>
+        <v>83.58999633789062</v>
       </c>
       <c r="D222" t="n">
-        <v>83.01000213623047</v>
+        <v>82.44999694824219</v>
       </c>
       <c r="E222" t="n">
-        <v>83.48999786376953</v>
+        <v>82.83999633789062</v>
       </c>
       <c r="F222" t="n">
-        <v>31641800</v>
+        <v>7059500</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B223" t="n">
-        <v>82.87000274658203</v>
+        <v>83.06999969482422</v>
       </c>
       <c r="C223" t="n">
-        <v>85.41000366210938</v>
+        <v>84.12000274658203</v>
       </c>
       <c r="D223" t="n">
-        <v>82.62999725341797</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="E223" t="n">
-        <v>85</v>
+        <v>83.23000335693359</v>
       </c>
       <c r="F223" t="n">
-        <v>31954300</v>
+        <v>10409000</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B224" t="n">
-        <v>83.5</v>
+        <v>83.44999694824219</v>
       </c>
       <c r="C224" t="n">
-        <v>83.5</v>
+        <v>83.94000244140625</v>
       </c>
       <c r="D224" t="n">
-        <v>80.23999786376953</v>
+        <v>82.51000213623047</v>
       </c>
       <c r="E224" t="n">
-        <v>80.65000152587891</v>
+        <v>83.68000030517578</v>
       </c>
       <c r="F224" t="n">
-        <v>36318900</v>
+        <v>10613200</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B225" t="n">
-        <v>81.83000183105469</v>
+        <v>83.95999908447266</v>
       </c>
       <c r="C225" t="n">
-        <v>83.59999847412109</v>
+        <v>84.05000305175781</v>
       </c>
       <c r="D225" t="n">
-        <v>81.05999755859375</v>
+        <v>82.23999786376953</v>
       </c>
       <c r="E225" t="n">
-        <v>83</v>
+        <v>83.15000152587891</v>
       </c>
       <c r="F225" t="n">
-        <v>22668800</v>
+        <v>12798900</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B226" t="n">
-        <v>81.01999664306641</v>
+        <v>82.81999969482422</v>
       </c>
       <c r="C226" t="n">
-        <v>81.27999877929688</v>
+        <v>84.27999877929688</v>
       </c>
       <c r="D226" t="n">
-        <v>80.16999816894531</v>
+        <v>82.37999725341797</v>
       </c>
       <c r="E226" t="n">
-        <v>80.80000305175781</v>
+        <v>84.01000213623047</v>
       </c>
       <c r="F226" t="n">
-        <v>20334400</v>
+        <v>20839400</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B227" t="n">
-        <v>82</v>
+        <v>81.69999694824219</v>
       </c>
       <c r="C227" t="n">
-        <v>82.20999908447266</v>
+        <v>82.25</v>
       </c>
       <c r="D227" t="n">
-        <v>80.84999847412109</v>
+        <v>80.58000183105469</v>
       </c>
       <c r="E227" t="n">
-        <v>81.44999694824219</v>
+        <v>82.12999725341797</v>
       </c>
       <c r="F227" t="n">
-        <v>15669300</v>
+        <v>16605900</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="B228" t="n">
-        <v>82.62999725341797</v>
+        <v>85</v>
       </c>
       <c r="C228" t="n">
-        <v>82.87999725341797</v>
+        <v>85.08000183105469</v>
       </c>
       <c r="D228" t="n">
-        <v>81.22000122070312</v>
+        <v>82.04000091552734</v>
       </c>
       <c r="E228" t="n">
-        <v>81.36000061035156</v>
+        <v>82.22000122070312</v>
       </c>
       <c r="F228" t="n">
-        <v>15156600</v>
+        <v>18457400</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="B229" t="n">
-        <v>83.09999847412109</v>
+        <v>81.79000091552734</v>
       </c>
       <c r="C229" t="n">
-        <v>83.13999938964844</v>
+        <v>83.79000091552734</v>
       </c>
       <c r="D229" t="n">
-        <v>81.84999847412109</v>
+        <v>81.79000091552734</v>
       </c>
       <c r="E229" t="n">
-        <v>82.33000183105469</v>
+        <v>83.61000061035156</v>
       </c>
       <c r="F229" t="n">
-        <v>11443900</v>
+        <v>19308800</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46167</v>
+        <v>46178</v>
       </c>
       <c r="B230" t="n">
-        <v>83.58999633789062</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="C230" t="n">
-        <v>83.58999633789062</v>
+        <v>80.79000091552734</v>
       </c>
       <c r="D230" t="n">
-        <v>82.44999694824219</v>
+        <v>78.33000183105469</v>
       </c>
       <c r="E230" t="n">
-        <v>82.83999633789062</v>
+        <v>80.79000091552734</v>
       </c>
       <c r="F230" t="n">
-        <v>7059500</v>
+        <v>23008500</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46181</v>
       </c>
       <c r="B231" t="n">
-        <v>83.06999969482422</v>
+        <v>78.06999969482422</v>
       </c>
       <c r="C231" t="n">
-        <v>84.12000274658203</v>
+        <v>79.27999877929688</v>
       </c>
       <c r="D231" t="n">
-        <v>82.30000305175781</v>
+        <v>77.31999969482422</v>
       </c>
       <c r="E231" t="n">
-        <v>83.23000335693359</v>
+        <v>78.91999816894531</v>
       </c>
       <c r="F231" t="n">
-        <v>10409000</v>
+        <v>15671500</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="B232" t="n">
-        <v>83.44999694824219</v>
+        <v>78.5</v>
       </c>
       <c r="C232" t="n">
-        <v>83.94000244140625</v>
+        <v>78.79000091552734</v>
       </c>
       <c r="D232" t="n">
-        <v>82.51000213623047</v>
+        <v>76.83000183105469</v>
       </c>
       <c r="E232" t="n">
-        <v>83.68000030517578</v>
+        <v>78.79000091552734</v>
       </c>
       <c r="F232" t="n">
-        <v>10613200</v>
+        <v>17523500</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="B233" t="n">
-        <v>83.95999908447266</v>
+        <v>77.69999694824219</v>
       </c>
       <c r="C233" t="n">
-        <v>84.05000305175781</v>
+        <v>78.15000152587891</v>
       </c>
       <c r="D233" t="n">
-        <v>82.23999786376953</v>
+        <v>77.19999694824219</v>
       </c>
       <c r="E233" t="n">
-        <v>83.15000152587891</v>
+        <v>77.91999816894531</v>
       </c>
       <c r="F233" t="n">
-        <v>12798900</v>
+        <v>12469100</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="B234" t="n">
-        <v>82.81999969482422</v>
+        <v>78.80000305175781</v>
       </c>
       <c r="C234" t="n">
-        <v>84.27999877929688</v>
+        <v>79.05000305175781</v>
       </c>
       <c r="D234" t="n">
-        <v>82.37999725341797</v>
+        <v>77.09999847412109</v>
       </c>
       <c r="E234" t="n">
-        <v>84.01000213623047</v>
+        <v>78.12000274658203</v>
       </c>
       <c r="F234" t="n">
-        <v>20839400</v>
+        <v>17725500</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="B235" t="n">
-        <v>81.69999694824219</v>
+        <v>79.16999816894531</v>
       </c>
       <c r="C235" t="n">
-        <v>82.25</v>
+        <v>79.80000305175781</v>
       </c>
       <c r="D235" t="n">
-        <v>80.58000183105469</v>
+        <v>78.12999725341797</v>
       </c>
       <c r="E235" t="n">
-        <v>82.12999725341797</v>
+        <v>78.66000366210938</v>
       </c>
       <c r="F235" t="n">
-        <v>16605900</v>
+        <v>12112600</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46188</v>
       </c>
       <c r="B236" t="n">
-        <v>85</v>
+        <v>81.16000366210938</v>
       </c>
       <c r="C236" t="n">
-        <v>85.08000183105469</v>
+        <v>82.73999786376953</v>
       </c>
       <c r="D236" t="n">
-        <v>82.04000091552734</v>
+        <v>80.65000152587891</v>
       </c>
       <c r="E236" t="n">
-        <v>82.22000122070312</v>
+        <v>80.77999877929688</v>
       </c>
       <c r="F236" t="n">
-        <v>18457400</v>
+        <v>22329400</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="B237" t="n">
-        <v>81.79000091552734</v>
+        <v>81.44000244140625</v>
       </c>
       <c r="C237" t="n">
-        <v>83.79000091552734</v>
+        <v>82.19000244140625</v>
       </c>
       <c r="D237" t="n">
-        <v>81.79000091552734</v>
+        <v>80.59999847412109</v>
       </c>
       <c r="E237" t="n">
-        <v>83.61000061035156</v>
+        <v>80.73999786376953</v>
       </c>
       <c r="F237" t="n">
-        <v>19308800</v>
+        <v>19713900</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="B238" t="n">
-        <v>78.69999694824219</v>
+        <v>79.77999877929688</v>
       </c>
       <c r="C238" t="n">
-        <v>80.79000091552734</v>
+        <v>81.33999633789062</v>
       </c>
       <c r="D238" t="n">
-        <v>78.33000183105469</v>
+        <v>79.26000213623047</v>
       </c>
       <c r="E238" t="n">
-        <v>80.79000091552734</v>
+        <v>80.34999847412109</v>
       </c>
       <c r="F238" t="n">
-        <v>23008500</v>
+        <v>20268200</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="B239" t="n">
-        <v>78.06999969482422</v>
+        <v>79.94000244140625</v>
       </c>
       <c r="C239" t="n">
-        <v>79.27999877929688</v>
+        <v>80.37999725341797</v>
       </c>
       <c r="D239" t="n">
-        <v>77.31999969482422</v>
+        <v>78.87999725341797</v>
       </c>
       <c r="E239" t="n">
-        <v>78.91999816894531</v>
+        <v>79.5</v>
       </c>
       <c r="F239" t="n">
-        <v>15671500</v>
+        <v>19651900</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46182</v>
+        <v>46192</v>
       </c>
       <c r="B240" t="n">
-        <v>78.5</v>
+        <v>80.75</v>
       </c>
       <c r="C240" t="n">
-        <v>78.79000091552734</v>
+        <v>81.06999969482422</v>
       </c>
       <c r="D240" t="n">
-        <v>76.83000183105469</v>
+        <v>79.5</v>
       </c>
       <c r="E240" t="n">
-        <v>78.79000091552734</v>
+        <v>79.68000030517578</v>
       </c>
       <c r="F240" t="n">
-        <v>17523500</v>
+        <v>26305900</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="B241" t="n">
-        <v>77.69999694824219</v>
+        <v>80.91000366210938</v>
       </c>
       <c r="C241" t="n">
-        <v>78.15000152587891</v>
+        <v>81.58000183105469</v>
       </c>
       <c r="D241" t="n">
-        <v>77.19999694824219</v>
+        <v>80.11000061035156</v>
       </c>
       <c r="E241" t="n">
-        <v>77.91999816894531</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="F241" t="n">
-        <v>12469100</v>
+        <v>18089300</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="B242" t="n">
-        <v>78.80000305175781</v>
+        <v>79.37999725341797</v>
       </c>
       <c r="C242" t="n">
-        <v>79.05000305175781</v>
+        <v>79.98000335693359</v>
       </c>
       <c r="D242" t="n">
-        <v>77.09999847412109</v>
+        <v>78.81999969482422</v>
       </c>
       <c r="E242" t="n">
-        <v>78.12000274658203</v>
+        <v>79.47000122070312</v>
       </c>
       <c r="F242" t="n">
-        <v>17725500</v>
+        <v>18415100</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="B243" t="n">
-        <v>79.16999816894531</v>
+        <v>77.73000335693359</v>
       </c>
       <c r="C243" t="n">
-        <v>79.80000305175781</v>
+        <v>78.86000061035156</v>
       </c>
       <c r="D243" t="n">
-        <v>78.12999725341797</v>
+        <v>77.16000366210938</v>
       </c>
       <c r="E243" t="n">
-        <v>78.66000366210938</v>
+        <v>78.55999755859375</v>
       </c>
       <c r="F243" t="n">
-        <v>12112600</v>
+        <v>22558900</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="B244" t="n">
-        <v>81.16000366210938</v>
+        <v>78.66000366210938</v>
       </c>
       <c r="C244" t="n">
-        <v>82.73999786376953</v>
+        <v>79.22000122070312</v>
       </c>
       <c r="D244" t="n">
-        <v>80.65000152587891</v>
+        <v>77.41999816894531</v>
       </c>
       <c r="E244" t="n">
-        <v>80.77999877929688</v>
+        <v>78.19999694824219</v>
       </c>
       <c r="F244" t="n">
-        <v>22329400</v>
+        <v>13882800</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="B245" t="n">
-        <v>81.44000244140625</v>
+        <v>78.15000152587891</v>
       </c>
       <c r="C245" t="n">
-        <v>82.19000244140625</v>
+        <v>78.87999725341797</v>
       </c>
       <c r="D245" t="n">
-        <v>80.59999847412109</v>
+        <v>77.91000366210938</v>
       </c>
       <c r="E245" t="n">
-        <v>80.73999786376953</v>
+        <v>78.18000030517578</v>
       </c>
       <c r="F245" t="n">
-        <v>19713900</v>
+        <v>25251100</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="B246" t="n">
-        <v>79.77999877929688</v>
+        <v>78.12999725341797</v>
       </c>
       <c r="C246" t="n">
-        <v>81.33999633789062</v>
+        <v>78.55999755859375</v>
       </c>
       <c r="D246" t="n">
-        <v>79.26000213623047</v>
+        <v>77.15000152587891</v>
       </c>
       <c r="E246" t="n">
-        <v>80.34999847412109</v>
+        <v>78.34999847412109</v>
       </c>
       <c r="F246" t="n">
-        <v>20268200</v>
+        <v>11791900</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>79.94000244140625</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C247" t="n">
-        <v>80.37999725341797</v>
+        <v>78.29000091552734</v>
       </c>
       <c r="D247" t="n">
-        <v>78.87999725341797</v>
+        <v>77.25</v>
       </c>
       <c r="E247" t="n">
-        <v>79.5</v>
+        <v>78.09999847412109</v>
       </c>
       <c r="F247" t="n">
-        <v>19651900</v>
+        <v>11289500</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46192</v>
+        <v>46204</v>
       </c>
       <c r="B248" t="n">
-        <v>80.75</v>
+        <v>77.97000122070312</v>
       </c>
       <c r="C248" t="n">
-        <v>81.06999969482422</v>
+        <v>78.91999816894531</v>
       </c>
       <c r="D248" t="n">
-        <v>79.5</v>
+        <v>77.04000091552734</v>
       </c>
       <c r="E248" t="n">
-        <v>79.68000030517578</v>
+        <v>77.08999633789062</v>
       </c>
       <c r="F248" t="n">
-        <v>26305900</v>
+        <v>15414700</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="B249" t="n">
-        <v>80.91000366210938</v>
+        <v>78.23999786376953</v>
       </c>
       <c r="C249" t="n">
-        <v>81.58000183105469</v>
+        <v>79.31999969482422</v>
       </c>
       <c r="D249" t="n">
-        <v>80.11000061035156</v>
+        <v>77.72000122070312</v>
       </c>
       <c r="E249" t="n">
-        <v>80.55000305175781</v>
+        <v>78.59999847412109</v>
       </c>
       <c r="F249" t="n">
-        <v>18089300</v>
+        <v>17199300</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46206</v>
       </c>
       <c r="B250" t="n">
-        <v>79.37999725341797</v>
+        <v>78.83999633789062</v>
       </c>
       <c r="C250" t="n">
-        <v>79.98000335693359</v>
+        <v>79.04000091552734</v>
       </c>
       <c r="D250" t="n">
-        <v>78.81999969482422</v>
+        <v>78.01000213623047</v>
       </c>
       <c r="E250" t="n">
-        <v>79.47000122070312</v>
+        <v>78.43000030517578</v>
       </c>
       <c r="F250" t="n">
-        <v>18415100</v>
+        <v>7793500</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="B251" t="n">
-        <v>77.73000335693359</v>
+        <v>77.79000091552734</v>
       </c>
       <c r="C251" t="n">
-        <v>78.86000061035156</v>
+        <v>78.77999877929688</v>
       </c>
       <c r="D251" t="n">
-        <v>77.16000366210938</v>
+        <v>77.5</v>
       </c>
       <c r="E251" t="n">
-        <v>78.55999755859375</v>
+        <v>78.29000091552734</v>
       </c>
       <c r="F251" t="n">
-        <v>22558900</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B252" t="n">
-        <v>78.52999877929688</v>
-      </c>
-      <c r="C252" t="n">
-        <v>79.22000122070312</v>
-      </c>
-      <c r="D252" t="n">
-        <v>77.41999816894531</v>
-      </c>
-      <c r="E252" t="n">
-        <v>78.19999694824219</v>
-      </c>
-      <c r="F252" t="n">
-        <v>11620700</v>
+        <v>12355500</v>
       </c>
     </row>
   </sheetData>
